--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B22" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B68" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B69" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B70" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B72" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B73" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Holly Humberstone - Cruel World (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B78" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B79" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B85" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B91" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B92" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B94" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B97" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B98" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B99" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B101" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B4" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B5" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B7" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B9" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B19" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B20" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B22" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
-        <v>4w ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4w ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B68" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B69" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B70" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B72" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B73" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Holly Humberstone - Cruel World (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B78" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B79" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B85" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B91" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B92" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B93" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B94" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B97" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B98" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B99" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B101" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-15</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H102" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L102" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Bottom Of Your Boots</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-15</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Dandelion</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G103" t="str">
-        <v>3:19</v>
+        <v>3:14</v>
       </c>
       <c r="H103" t="str">
-        <v>Ella Langley</v>
+        <v>DANNA</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L103" t="str">
-        <v>Bottom Of Your Boots - Ella Langley</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>RUNWAY</v>
+        <v>Bottom Of Your Boots</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/runway/1891472591</v>
+        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-15</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>RUNWAY - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G104" t="str">
-        <v>2:51</v>
+        <v>3:19</v>
       </c>
       <c r="H104" t="str">
-        <v>Lady Gaga</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/runway/1891472590</v>
+        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
       </c>
       <c r="L104" t="str">
-        <v>RUNWAY - Lady Gaga</v>
+        <v>Bottom Of Your Boots - Ella Langley</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Back and Forth (feat. Missy Elliott)</v>
+        <v>RUNWAY</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
+        <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-15</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Kehlani</v>
+        <v>RUNWAY - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:34</v>
+        <v>2:51</v>
       </c>
       <c r="H105" t="str">
-        <v>Kehlani</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
+        <v>https://music.apple.com/us/album/runway/1891472590</v>
       </c>
       <c r="L105" t="str">
-        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
+        <v>RUNWAY - Lady Gaga</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mr. Know It All</v>
+        <v>Back and Forth (feat. Missy Elliott)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
+        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-15</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Mr. Know It All - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G106" t="str">
-        <v>3:18</v>
+        <v>3:34</v>
       </c>
       <c r="H106" t="str">
-        <v>Teddy Swims</v>
+        <v>Kehlani</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
+        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
       </c>
       <c r="L106" t="str">
-        <v>Mr. Know It All - Teddy Swims</v>
+        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Bad Angel</v>
+        <v>Mr. Know It All</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
+        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-15</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Bad Angel - Single</v>
+        <v>Mr. Know It All - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:33</v>
+        <v>3:18</v>
       </c>
       <c r="H107" t="str">
-        <v>Anyma</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
+        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
       </c>
       <c r="L107" t="str">
-        <v>Bad Angel - Anyma</v>
+        <v>Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Step (feat. Swizz Beatz)</v>
+        <v>Bad Angel</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
+        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-15</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>10 Til' Midnight</v>
+        <v>Bad Angel - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:34</v>
+        <v>2:33</v>
       </c>
       <c r="H108" t="str">
-        <v>Snoop Dogg</v>
+        <v>Anyma</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
+        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
       </c>
       <c r="L108" t="str">
-        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
+        <v>Bad Angel - Anyma</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Sweet Hallelujah</v>
+        <v>Step (feat. Swizz Beatz)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
+        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-15</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Sweet Hallelujah - Single</v>
+        <v>10 Til' Midnight</v>
       </c>
       <c r="G109" t="str">
-        <v>3:02</v>
+        <v>3:34</v>
       </c>
       <c r="H109" t="str">
-        <v>Royel Otis</v>
+        <v>Snoop Dogg</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
+        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
+        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
       </c>
       <c r="L109" t="str">
-        <v>Sweet Hallelujah - Royel Otis</v>
+        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Beauty Pageant</v>
+        <v>Sweet Hallelujah</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
+        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-15</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cruel World</v>
+        <v>Sweet Hallelujah - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H110" t="str">
-        <v>Holly Humberstone</v>
+        <v>Royel Otis</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
+        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
       </c>
       <c r="L110" t="str">
-        <v>Beauty Pageant - Holly Humberstone</v>
+        <v>Sweet Hallelujah - Royel Otis</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PINKY UP</v>
+        <v>Beauty Pageant</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-15</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>PINKY UP - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G111" t="str">
-        <v>2:11</v>
+        <v>3:15</v>
       </c>
       <c r="H111" t="str">
-        <v>KATSEYE</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
       </c>
       <c r="L111" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>Beauty Pageant - Holly Humberstone</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>i just get worse</v>
+        <v>PINKY UP</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-15</v>
@@ -4631,25 +4631,25 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>i just get worse - Single</v>
+        <v>PINKY UP - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>2:11</v>
       </c>
       <c r="H112" t="str">
-        <v>Kevian Kraemer</v>
+        <v>KATSEYE</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
       </c>
       <c r="L112" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>PINKY UP - KATSEYE</v>
       </c>
     </row>
     <row r="113">
@@ -4692,13 +4692,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Ember</v>
+        <v>i just get worse</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-15</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G114" t="str">
         <v>3:25</v>
       </c>
       <c r="H114" t="str">
-        <v>Iceage</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L114" t="str">
-        <v>Ember - Iceage</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-15</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G115" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H115" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L115" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Turnaround</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-15</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Labrinth</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L116" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Madwoman</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-15</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:59</v>
+        <v>3:05</v>
       </c>
       <c r="H117" t="str">
-        <v>Laufey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L117" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Madwoman</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-15</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G118" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H118" t="str">
-        <v>Hilary Duff</v>
+        <v>Laufey</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L118" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>One of Them</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-15</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>One of Them - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H119" t="str">
-        <v>DJ Khaled</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L119" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-15</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H120" t="str">
-        <v>Bossman Dlow</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L120" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>stuck</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-15</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>ghosted - EP</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G121" t="str">
-        <v>2:41</v>
+        <v>2:49</v>
       </c>
       <c r="H121" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L121" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>De Lejitos</v>
+        <v>stuck</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-15</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>De Lejitos - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H122" t="str">
-        <v>Jay Wheeler</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L122" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Echo</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-15</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Echo - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H123" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L123" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Where We Go</v>
+        <v>Echo</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-15</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Where We Go - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H124" t="str">
-        <v>Marshmello</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L124" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Where We Go</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-15</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Apambichao</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H125" t="str">
-        <v>Manuel Turizo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L125" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Of All People</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-15</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Apambichao</v>
       </c>
       <c r="G126" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H126" t="str">
-        <v>Foo Fighters</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L126" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Waves of You</v>
+        <v>Of All People</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-15</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Waves of You - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G127" t="str">
-        <v>3:15</v>
+        <v>2:34</v>
       </c>
       <c r="H127" t="str">
-        <v>After Hours</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L127" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-15</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H128" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L128" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-15</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L129" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-15</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G130" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H130" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L130" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-15</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H131" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L131" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-15</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H132" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L132" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-15</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>5:06</v>
+        <v>3:06</v>
       </c>
       <c r="H133" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L133" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-15</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G134" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H134" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L134" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-15</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G135" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H135" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L135" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-15</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G136" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H136" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L136" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-15</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L137" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Woman I Am</v>
+        <v>side slider</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-15</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>SE9</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G138" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H138" t="str">
-        <v>Skye Newman</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L138" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Bubee</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-15</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Bubee - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G139" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H139" t="str">
-        <v>ILLIT</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L139" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Good Morning</v>
+        <v>Bubee</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-15</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>24</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G140" t="str">
         <v>3:02</v>
       </c>
       <c r="H140" t="str">
-        <v>Alexis Ffrench</v>
+        <v>ILLIT</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L140" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Positano</v>
+        <v>Good Morning</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-15</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>24</v>
       </c>
       <c r="G141" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H141" t="str">
-        <v>Stephan Moccio</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L141" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>sophie</v>
+        <v>Positano</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-15</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G142" t="str">
-        <v>2:36</v>
+        <v>3:27</v>
       </c>
       <c r="H142" t="str">
-        <v>kenzie</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L142" t="str">
-        <v>sophie - kenzie</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>kiss goodbye</v>
+        <v>sophie</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-15</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>2:36</v>
       </c>
       <c r="H143" t="str">
-        <v>The Two Lips</v>
+        <v>kenzie</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L143" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ENTRÉGAME</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-15</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:08</v>
+        <v>2:43</v>
       </c>
       <c r="H144" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L144" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>EL SENTRITA</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-15</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>ETERNO</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G145" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H145" t="str">
-        <v>Calle 24</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L145" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-15</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>DAWN PATROL</v>
+        <v>ETERNO</v>
       </c>
       <c r="G146" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H146" t="str">
-        <v>PARTY WAVE</v>
+        <v>Calle 24</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L146" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Formation</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-15</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Formation - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G147" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Adekunle Gold</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L147" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Who Will You Follow</v>
+        <v>Formation</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-15</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Sanctuary</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:55</v>
+        <v>2:36</v>
       </c>
       <c r="H148" t="str">
-        <v>Evanescence</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L148" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>That's When You Know</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-15</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G149" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H149" t="str">
-        <v>Kygo</v>
+        <v>Evanescence</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L149" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drinking Game</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-15</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Drinking Game - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H150" t="str">
-        <v>Warren Zeiders</v>
+        <v>Kygo</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L150" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Anything But Me</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-15</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>In The Feeling</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>4:59</v>
+        <v>2:50</v>
       </c>
       <c r="H151" t="str">
-        <v>Owen Riegling</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L151" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>American Dream</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-15</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>American Dream - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G152" t="str">
-        <v>4:27</v>
+        <v>4:59</v>
       </c>
       <c r="H152" t="str">
-        <v>Alabama Shakes</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L152" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Already There</v>
+        <v>American Dream</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-15</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Victory Garden</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H153" t="str">
-        <v>Young the Giant</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L153" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Already There</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-15</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>KINDA HARD</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G154" t="str">
-        <v>2:47</v>
+        <v>3:50</v>
       </c>
       <c r="H154" t="str">
-        <v>Bilmuri</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L154" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Alone For A Year</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-15</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Joy Next Door</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G155" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H155" t="str">
-        <v>The Maine</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L155" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Bring Home My Man</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-15</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G156" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H156" t="str">
-        <v>Maya Hawke</v>
+        <v>The Maine</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L156" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SUPERMAN</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-15</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G157" t="str">
-        <v>3:24</v>
+        <v>4:22</v>
       </c>
       <c r="H157" t="str">
-        <v>South Arcade</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L157" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>1989</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-15</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>1989 - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:34</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Nightly</v>
+        <v>South Arcade</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L158" t="str">
-        <v>1989 - Nightly</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>waste your pain</v>
+        <v>1989</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-15</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>waste your pain - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:23</v>
+        <v>2:34</v>
       </c>
       <c r="H159" t="str">
-        <v>Cruz Beckham</v>
+        <v>Nightly</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L159" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Strangers</v>
+        <v>waste your pain</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-15</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:44</v>
+        <v>2:23</v>
       </c>
       <c r="H160" t="str">
-        <v>Tink</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L160" t="str">
-        <v>Strangers - Tink</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Strangers</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-15</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>2:44</v>
       </c>
       <c r="H161" t="str">
-        <v>Tiny Habits</v>
+        <v>Tink</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L161" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SAME SH!T</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-15</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:13</v>
+        <v>2:45</v>
       </c>
       <c r="H162" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L162" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-15</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>The End is Not the End</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H163" t="str">
-        <v>Atreyu</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L163" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Heal</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-15</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Heal - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G164" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H164" t="str">
-        <v>HAYLA</v>
+        <v>Atreyu</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L164" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Free</v>
+        <v>Heal</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-15</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H165" t="str">
-        <v>Simone Ashley</v>
+        <v>HAYLA</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L165" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cállate</v>
+        <v>Free</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-15</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>1:59</v>
+        <v>4:13</v>
       </c>
       <c r="H166" t="str">
-        <v>Dua Saleh</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L166" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Raindrops</v>
+        <v>Cállate</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-15</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Raindrops - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G167" t="str">
-        <v>3:34</v>
+        <v>1:59</v>
       </c>
       <c r="H167" t="str">
-        <v>Rick Astley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L167" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>WORK OF ART</v>
+        <v>Raindrops</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-15</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>PRODIGY</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H168" t="str">
-        <v>Tkandz</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L168" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Scottie Pippen</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-15</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G169" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H169" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tkandz</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L169" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Damn Good Actress</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-15</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:49</v>
+        <v>2:34</v>
       </c>
       <c r="H170" t="str">
-        <v>Tiffany Stringer</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L170" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Ricota</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-15</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Ricota - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:25</v>
+        <v>2:49</v>
       </c>
       <c r="H171" t="str">
-        <v>ZULAN</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L171" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Kissing The Ground</v>
+        <v>Ricota</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-15</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:50</v>
+        <v>2:25</v>
       </c>
       <c r="H172" t="str">
-        <v>Nell Mescal</v>
+        <v>ZULAN</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L172" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Joy</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-15</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>All In Now</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:41</v>
+        <v>3:50</v>
       </c>
       <c r="H173" t="str">
-        <v>Dogstar</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L173" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Amor Bonito</v>
+        <v>Joy</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-15</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>All In Now</v>
       </c>
       <c r="G174" t="str">
-        <v>2:44</v>
+        <v>3:41</v>
       </c>
       <c r="H174" t="str">
-        <v>Kany García</v>
+        <v>Dogstar</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L174" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Patchwork</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-15</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Patchwork - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G175" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H175" t="str">
-        <v>Carlita</v>
+        <v>Kany García</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L175" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>She's A Devil</v>
+        <v>Patchwork</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-15</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:24</v>
+        <v>3:07</v>
       </c>
       <c r="H176" t="str">
-        <v>Layton Giordani</v>
+        <v>Carlita</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L176" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Do It All Alone</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-15</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H177" t="str">
-        <v>Rend Collective</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L177" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Time</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-15</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Time - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:20</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>David Leonard</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L178" t="str">
-        <v>Time - David Leonard</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Andamos Ready</v>
+        <v>Time</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-15</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:10</v>
+        <v>3:20</v>
       </c>
       <c r="H179" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>David Leonard</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L179" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Van y Vienen</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-15</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H180" t="str">
-        <v>El Fantasma</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L180" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>No Vuelvas</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-15</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Majo Aguilar</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L181" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>RUNNIN</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-15</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>RUNNIN - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>3:46</v>
       </c>
       <c r="H182" t="str">
-        <v>RUA YOUNG</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L182" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Talk You Through It</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-15</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H183" t="str">
-        <v>Kenyon Dixon</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L183" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Partners in Crime</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-15</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Born to Kill</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H184" t="str">
-        <v>Social Distortion</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L184" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Change your mind</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-15</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Change your mind - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G185" t="str">
-        <v>3:21</v>
+        <v>3:50</v>
       </c>
       <c r="H185" t="str">
-        <v>Casper Sage</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L185" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Change your mind</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-15</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H186" t="str">
-        <v>The Franklin Electric</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L186" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-15</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Train on the Island</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:17</v>
+        <v>3:29</v>
       </c>
       <c r="H187" t="str">
-        <v>Aldous Harding</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L187" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lover</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-15</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lover - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H188" t="str">
-        <v>Juke Ross</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L188" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>pink moon</v>
+        <v>Lover</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-15</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H189" t="str">
-        <v>runo plum</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L189" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Summer</v>
+        <v>pink moon</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-15</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Summer - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G190" t="str">
         <v>3:21</v>
       </c>
       <c r="H190" t="str">
-        <v>Tasha</v>
+        <v>runo plum</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L190" t="str">
-        <v>Summer - Tasha</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Summer</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-15</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Nara's Room</v>
+        <v>Tasha</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L191" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fabienk</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-15</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Vol.II</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G192" t="str">
-        <v>6:31</v>
+        <v>4:20</v>
       </c>
       <c r="H192" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L192" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>My Girl</v>
+        <v>Fabienk</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-15</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Soren - EP</v>
+        <v>Vol.II</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>6:31</v>
       </c>
       <c r="H193" t="str">
-        <v>Orca</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L193" t="str">
-        <v>My Girl - Orca</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bone Structure</v>
+        <v>My Girl</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-15</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>3:01</v>
+        <v>3:45</v>
       </c>
       <c r="H194" t="str">
-        <v>Dolder</v>
+        <v>Orca</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L194" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Turning Into Us</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-15</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H195" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Dolder</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L195" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-15</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:00</v>
+        <v>3:30</v>
       </c>
       <c r="H196" t="str">
-        <v>Osé</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L196" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fright</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-15</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Fright - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H197" t="str">
-        <v>Creepy Nuts</v>
+        <v>Osé</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L197" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Smoking In Bed</v>
+        <v>Fright</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-15</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H198" t="str">
-        <v>The Bends</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L198" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>The Dissonant Void</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-15</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H199" t="str">
-        <v>At The Gates</v>
+        <v>The Bends</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L199" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-15</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G200" t="str">
-        <v>3:51</v>
+        <v>2:47</v>
       </c>
       <c r="H200" t="str">
-        <v>Melvins</v>
+        <v>At The Gates</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L200" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>4:46</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -1275,7 +1275,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G25" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B22" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 weeks ago</v>
+        <v>4w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B68" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B69" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B70" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B72" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B73" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Holly Humberstone - Cruel World (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B78" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B79" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B85" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B91" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B92" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B94" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B97" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B98" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B99" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B101" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1 month ago</v>
+        <v>1mo ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B4" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B5" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B7" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B9" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B13" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B14" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B16" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B19" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B20" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B22" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B24" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B25" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B29" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B30" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B31" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B33" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B35" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B36" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B41" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B42" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B43" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B45" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B48" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B50" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B53" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B54" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B58" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=033viNHogN4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B60" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B62" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4w ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B63" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Grace Enger - Give A Little (Live Performance)</v>
       </c>
       <c r="B64" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
       </c>
       <c r="B68" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>SIENNA SPIRO - The Visitor</v>
       </c>
       <c r="B69" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
       </c>
       <c r="B70" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Martin Garrix - Catharina (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Baby Queen - Feel Something (Official Visualiser)</v>
       </c>
       <c r="B72" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>HAUSER - Hungarian Dance No. 5</v>
       </c>
       <c r="B73" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Holly Humberstone - Cruel World (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Rick Astley - Waiting On You (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
       </c>
       <c r="B78" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Bishop Briggs - River (10 Years Later)</v>
       </c>
       <c r="B79" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
       </c>
       <c r="B81" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Allison Russell - Rainbows (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>We Three - Love Who You Love (Official Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>paris jackson - zombies in love</v>
       </c>
       <c r="B85" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kane Brown - Woman (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Malcolm Todd - Breathe (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
       </c>
       <c r="B91" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>aron! - Wonderful Thing (Piano)</v>
       </c>
       <c r="B92" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
       </c>
       <c r="B93" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Sunday (1994) - The Fairground</v>
       </c>
       <c r="B94" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Owen Riegling - In The Feeling (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Maverick Sabre - 8 Stages</v>
       </c>
       <c r="B97" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Amanda Jordan - What Else Is New</v>
       </c>
       <c r="B98" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
       </c>
       <c r="B99" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
       </c>
       <c r="B101" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1mo ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Ocean Alley</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>RAYE</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Take That</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B7" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Armik</v>
+        <v>kenzie</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Switchfoot</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Peter Gabriel</v>
+        <v>Laufey</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Sarah Julia</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Chris Norman</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-16</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Alan Walker</v>
+        <v>Evanescence</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-16</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Charlie Puth</v>
+        <v>elijah woods</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-16</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Miley Cyrus</v>
+        <v>colby!</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-16</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Conan Gray</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-16</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Charlie Puth</v>
+        <v>aron!</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B17" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Kylie Morgan</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B18" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B19" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Angelina Mango</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Julio Iglesias</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Loreen</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Jessie Ware</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Holly Humberstone and Life is Strange</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone and Life is Strange</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B25" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Ella Langley</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Eagles</v>
+        <v>We Three</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Moody Joody</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jackson Dean</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Madison Cunningham</v>
+        <v>METTE</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>mary in the junkyard</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B32" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Adam Sanders</v>
+        <v>NewDad</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Danna</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>twocolors</v>
+        <v>florencemachine</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B35" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Prince</v>
+        <v>Kungs</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B37" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>RAYE</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>The Warning</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B39" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Pentatonix</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Tenille Townes</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Jessie Ware</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Niall Horan</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B44" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Jackson Dean</v>
+        <v>RAYE</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Foo Fighters</v>
+        <v>Take That</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Armik</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Ella Langley</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Cannons</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Luke Combs</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Nessa Barrett</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B53" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>aron!</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B54" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>DMA'S</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B56" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Nick Carter</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B59" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Carly Pearce</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-16</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>OneRepublic</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-16</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Loreen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video]</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B62" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=NaieFTTcUAY</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-16</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Armin van Buuren</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Armin van Buuren - Longing (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006)</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>1 month ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=QkQe7SctWRs</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-16</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>1 month ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>David Gilmour</v>
+        <v>Holly Humberstone and Life is Strange</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>David Gilmour - Comfortably Numb (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone and Life is Strange</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B64" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GPEqFR5HPDk</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Grace Enger</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Grace Enger - Give A Little (Live Performance) - Grace Enger</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B65" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=ymPWy3XH3WA</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Tucker Wetmore</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Tucker Wetmore - Sunburn (Official Visualizer) - Tucker Wetmore</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B66" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=lyuE94W1WIc</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>NathanEvanss</v>
+        <v>Eagles</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nathan Evans x Saint PHNX - Happy Place (Official Acoustic Video) - NathanEvanss</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=byJV11xY2dA</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Freya Ridings</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Freya Ridings - I Have Always Loved You (Official Video) - Freya Ridings</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=y8hp0FZqua0</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-16</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>David Gilmour</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>David Gilmour - High Hopes (AOL Sessions, NYC 2006) - David Gilmour</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SIENNA SPIRO - The Visitor</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=5Wq1iDyEjF8</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-16</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>SIENNA SPIRO - The Visitor - SIENNA SPIRO</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B70" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=LP6rz3x_JXc</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-16</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Jonas Brothers and Demi Lovato</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jonas Brothers ft. Demi Lovato - Wouldn't Change a Thing (Live from MetLife Stadium) - Jonas Brothers and Demi Lovato</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Martin Garrix - Catharina (Official Video)</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B71" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=G00dmXhboaw</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-16</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Martin Garrix</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Martin Garrix - Catharina (Official Video) - Martin Garrix</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=PUst-aAw7iQ</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-16</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Baby Queen</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Baby Queen - Feel Something (Official Visualiser) - Baby Queen</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HAUSER - Hungarian Dance No. 5</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
       </c>
       <c r="B73" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bT9VpXvFHHM</v>
+        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-16</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>HAUSER</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>HAUSER - Hungarian Dance No. 5 - HAUSER</v>
+        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Holly Humberstone - Cruel World (Official Video)</v>
+        <v>twocolors – Mad World (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=Oty-POynR6k</v>
+        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-16</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Holly Humberstone</v>
+        <v>twocolors</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Holly Humberstone - Cruel World (Official Video) - Holly Humberstone</v>
+        <v>twocolors – Mad World (Official Video) - twocolors</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video)</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
       </c>
       <c r="B75" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=0A3UZGADJDk</v>
+        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-16</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Goo Goo Dolls</v>
+        <v>CamelPhat and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Goo Goo Dolls - Misery (Official Lyric Video) - Goo Goo Dolls</v>
+        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Rick Astley - Waiting On You (Official Video)</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
       </c>
       <c r="B76" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=zRVjZ2DJ9Cg</v>
+        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Rick Astley</v>
+        <v>Prince</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Rick Astley - Waiting On You (Official Video) - Rick Astley</v>
+        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video)</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Oo3elzPt_qM</v>
+        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Alan Walker and Emyrson Flora</v>
+        <v>RAYE</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Lyric Video) - Alan Walker and Emyrson Flora</v>
+        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official)</v>
+        <v>The Warning - Kerosene (Performance Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=IpF37Cwf4kM</v>
+        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-16</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Jessie J</v>
+        <v>The Warning</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jessie J, Jools Holland - My Way (Live at Jools' Annual Hootenanny) (Official) - Jessie J</v>
+        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bishop Briggs - River (10 Years Later)</v>
+        <v>Pentatonix - Heaven On Earth (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=mnjnaz19lTo</v>
+        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-16</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Bishop Briggs</v>
+        <v>Pentatonix</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bishop Briggs - River (10 Years Later) - Bishop Briggs</v>
+        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video)</v>
+        <v>Tenille Townes - we could use a little more (Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ykrRgec42_c</v>
+        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-16</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Dean Lewis</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Dean Lewis - Enjoy It While It Lasts (Official Lyric Video) - Dean Lewis</v>
+        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video]</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
       </c>
       <c r="B81" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=yjL2pQcW-QU</v>
+        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Chris Janson and Official David Lee Murphy</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Chris Janson – Fun (feat. David Lee Murphy) [Official Music Video] - Chris Janson and Official David Lee Murphy</v>
+        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video)</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
       </c>
       <c r="B82" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=mj4efhy6n0o</v>
+        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Luke Combs</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Luke Combs - I Ain't No Cowboy (Official Studio Video) - Luke Combs</v>
+        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Allison Russell - Rainbows (Official Video)</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
       </c>
       <c r="B83" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=4KfGxyjIOG0</v>
+        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Allison Russell</v>
+        <v>John Summit and Major Lazer Official</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Allison Russell - Rainbows (Official Video) - Allison Russell</v>
+        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>We Three - Love Who You Love (Official Audio)</v>
+        <v>Stephen Stanley - Change (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=ufl578qog_U</v>
+        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>We Three</v>
+        <v>Stephen Stanley Music</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>We Three - Love Who You Love (Official Audio) - We Three</v>
+        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>paris jackson - zombies in love</v>
+        <v>Jackson Dean - Hey Mississippi</v>
       </c>
       <c r="B85" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=5LlErbOOUb8</v>
+        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>paris jackson</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>paris jackson - zombies in love - paris jackson</v>
+        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Kane Brown - Woman (Official Music Video)</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=AuifemOMjGU</v>
+        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Kane Brown</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Kane Brown - Woman (Official Music Video) - Kane Brown</v>
+        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video)</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=L41anOxYurk</v>
+        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Lainey Wilson</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Official Video) - Lainey Wilson</v>
+        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Malcolm Todd - Breathe (Official Video)</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=g1uEqR5eFMo</v>
+        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Malcolm Todd</v>
+        <v>Billy Raffoul and Booshle G.</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Malcolm Todd - Breathe (Official Video) - Malcolm Todd</v>
+        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video)</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=puwLnJ7bb9o</v>
+        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Carly Pearce and Riley Green</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Official Music Video) - Carly Pearce and Riley Green</v>
+        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer)</v>
+        <v>Cannons - Light as a Feather (Official Visualizer)</v>
       </c>
       <c r="B90" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=0YZC_HyMiHk</v>
+        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-16</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Kungs</v>
+        <v>Cannons</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Kungs, Boys Noize - Get Away (Visualizer) - Kungs</v>
+        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=FJx7BWemu4g</v>
+        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-16</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Sunday (1994)</v>
+        <v>Luke Combs</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sunday (1994) - Darling, I've Done This Dance Before - Sunday (1994)</v>
+        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>aron! - Wonderful Thing (Piano)</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
       </c>
       <c r="B92" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=WZiw6TxnLeg</v>
+        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-16</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>aron!</v>
+        <v>Nessa Barrett</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>aron! - Wonderful Thing (Piano) - aron!</v>
+        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio)</v>
+        <v>aron! - Wonderful Thing (Laundry Day)</v>
       </c>
       <c r="B93" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=XXO-9GNSip0</v>
+        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-16</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Colinstoughmusic</v>
+        <v>aron!</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Colin Stough - 21 Year Old Man Blues (Official Audio) - Colinstoughmusic</v>
+        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sunday (1994) - The Fairground</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
       </c>
       <c r="B94" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=m-E-PmdulbI</v>
+        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-16</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Sunday (1994)</v>
+        <v>Alessia Cara and Nelly Furtado</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sunday (1994) - The Fairground - Sunday (1994)</v>
+        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer)</v>
+        <v>DMA'S - My Baby's Place (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=ouClRTJoiyU</v>
+        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-16</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Owen Riegling</v>
+        <v>DMA'S</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Owen Riegling - In The Feeling (Visualizer) - Owen Riegling</v>
+        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video)</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=gZBHv4XCLVo</v>
+        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-16</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>1 month ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>LANY</v>
+        <v>Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>LANY - When Did You Stop Loving Me? (Official Live Video) - LANY</v>
+        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Maverick Sabre - 8 Stages</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=023U8zkDG9c</v>
+        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Maverick Sabre</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Maverick Sabre - 8 Stages - Maverick Sabre</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Amanda Jordan - What Else Is New</v>
+        <v>Nick Carter - Love Life Tragedy</v>
       </c>
       <c r="B98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=mUr2oC6DDc4</v>
+        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Amanda Jordan</v>
+        <v>Nick Carter</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Amanda Jordan - What Else Is New - Amanda Jordan</v>
+        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=qV91x2YT9zI</v>
+        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Beabadoobee</v>
+        <v>Carly Pearce</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>beabadoobee - All I Did Was Dream Of You (Official Video) ft. The Marías - Beabadoobee</v>
+        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video)</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
       </c>
       <c r="B100" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=cVMV_jD8H-4</v>
+        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Spacey Jane</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Spacey Jane - Do You Really Love Her (Official Music Video) - Spacey Jane</v>
+        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
       </c>
       <c r="B101" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=JHGHFdEyidg</v>
+        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>1 month ago</v>
+        <v>4 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Spotify and Zara Larsson</v>
+        <v>Jonas Blue and The Real Salif Keita</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Zara Larsson - Midnight Sun (Live) | Spotify Live Room - Spotify and Zara Larsson</v>
+        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
       </c>
     </row>
     <row r="102">
@@ -5642,13 +5642,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Woman I Am</v>
+        <v>Bubee</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>SE9</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H139" t="str">
-        <v>Skye Newman</v>
+        <v>ILLIT</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L139" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Bubee</v>
+        <v>Good Morning</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Bubee - Single</v>
+        <v>24</v>
       </c>
       <c r="G140" t="str">
         <v>3:02</v>
       </c>
       <c r="H140" t="str">
-        <v>ILLIT</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L140" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Good Morning</v>
+        <v>Positano</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>24</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G141" t="str">
-        <v>3:02</v>
+        <v>3:27</v>
       </c>
       <c r="H141" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L141" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Positano</v>
+        <v>sophie</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G142" t="str">
-        <v>3:27</v>
+        <v>2:36</v>
       </c>
       <c r="H142" t="str">
-        <v>Stephan Moccio</v>
+        <v>kenzie</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L142" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>sophie</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>notes from the in between - EP</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:36</v>
+        <v>2:43</v>
       </c>
       <c r="H143" t="str">
-        <v>kenzie</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L143" t="str">
-        <v>sophie - kenzie</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>kiss goodbye</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G144" t="str">
-        <v>2:43</v>
+        <v>3:08</v>
       </c>
       <c r="H144" t="str">
-        <v>The Two Lips</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L144" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ENTRÉGAME</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>ETERNO</v>
       </c>
       <c r="G145" t="str">
-        <v>3:08</v>
+        <v>2:57</v>
       </c>
       <c r="H145" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>Calle 24</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L145" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>EL SENTRITA</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ETERNO</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G146" t="str">
-        <v>2:57</v>
+        <v>2:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Calle 24</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L146" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>Formation</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>DAWN PATROL</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:39</v>
+        <v>2:36</v>
       </c>
       <c r="H147" t="str">
-        <v>PARTY WAVE</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L147" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Formation</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Formation - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G148" t="str">
-        <v>2:36</v>
+        <v>3:55</v>
       </c>
       <c r="H148" t="str">
-        <v>Adekunle Gold</v>
+        <v>Evanescence</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L148" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Who Will You Follow</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Sanctuary</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:55</v>
+        <v>3:13</v>
       </c>
       <c r="H149" t="str">
-        <v>Evanescence</v>
+        <v>Kygo</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L149" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>That's When You Know</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:13</v>
+        <v>2:50</v>
       </c>
       <c r="H150" t="str">
-        <v>Kygo</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L150" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Drinking Game</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Drinking Game - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G151" t="str">
-        <v>2:50</v>
+        <v>4:59</v>
       </c>
       <c r="H151" t="str">
-        <v>Warren Zeiders</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L151" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Anything But Me</v>
+        <v>American Dream</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>In The Feeling</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>4:59</v>
+        <v>4:27</v>
       </c>
       <c r="H152" t="str">
-        <v>Owen Riegling</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L152" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>American Dream</v>
+        <v>Already There</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>American Dream - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G153" t="str">
-        <v>4:27</v>
+        <v>3:50</v>
       </c>
       <c r="H153" t="str">
-        <v>Alabama Shakes</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L153" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Already There</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Victory Garden</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G154" t="str">
-        <v>3:50</v>
+        <v>2:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Young the Giant</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L154" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>KINDA HARD</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G155" t="str">
-        <v>2:47</v>
+        <v>3:22</v>
       </c>
       <c r="H155" t="str">
-        <v>Bilmuri</v>
+        <v>The Maine</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L155" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Alone For A Year</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Joy Next Door</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G156" t="str">
-        <v>3:22</v>
+        <v>4:22</v>
       </c>
       <c r="H156" t="str">
-        <v>The Maine</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L156" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bring Home My Man</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>4:22</v>
+        <v>3:24</v>
       </c>
       <c r="H157" t="str">
-        <v>Maya Hawke</v>
+        <v>South Arcade</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L157" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SUPERMAN</v>
+        <v>1989</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:24</v>
+        <v>2:34</v>
       </c>
       <c r="H158" t="str">
-        <v>South Arcade</v>
+        <v>Nightly</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L158" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>1989</v>
+        <v>waste your pain</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>1989 - Single</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:34</v>
+        <v>2:23</v>
       </c>
       <c r="H159" t="str">
-        <v>Nightly</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L159" t="str">
-        <v>1989 - Nightly</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>waste your pain</v>
+        <v>Strangers</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>waste your pain - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G160" t="str">
-        <v>2:23</v>
+        <v>2:44</v>
       </c>
       <c r="H160" t="str">
-        <v>Cruz Beckham</v>
+        <v>Tink</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L160" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Strangers</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:44</v>
+        <v>2:45</v>
       </c>
       <c r="H161" t="str">
-        <v>Tink</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L161" t="str">
-        <v>Strangers - Tink</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Right In Front Of Me</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:45</v>
+        <v>3:13</v>
       </c>
       <c r="H162" t="str">
-        <v>Tiny Habits</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L162" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SAME SH!T</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G163" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H163" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Atreyu</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L163" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Heal</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>The End is Not the End</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:12</v>
+        <v>3:26</v>
       </c>
       <c r="H164" t="str">
-        <v>Atreyu</v>
+        <v>HAYLA</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L164" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Heal</v>
+        <v>Free</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Heal - Single</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>3:26</v>
+        <v>4:13</v>
       </c>
       <c r="H165" t="str">
-        <v>HAYLA</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L165" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Free</v>
+        <v>Cállate</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G166" t="str">
-        <v>4:13</v>
+        <v>1:59</v>
       </c>
       <c r="H166" t="str">
-        <v>Simone Ashley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L166" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Cállate</v>
+        <v>Raindrops</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>1:59</v>
+        <v>3:34</v>
       </c>
       <c r="H167" t="str">
-        <v>Dua Saleh</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L167" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Raindrops</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Raindrops - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G168" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H168" t="str">
-        <v>Rick Astley</v>
+        <v>Tkandz</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L168" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>WORK OF ART</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>PRODIGY</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H169" t="str">
-        <v>Tkandz</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L169" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Scottie Pippen</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:34</v>
+        <v>2:49</v>
       </c>
       <c r="H170" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L170" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Damn Good Actress</v>
+        <v>Ricota</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:49</v>
+        <v>2:25</v>
       </c>
       <c r="H171" t="str">
-        <v>Tiffany Stringer</v>
+        <v>ZULAN</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L171" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Ricota</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Ricota - Single</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:25</v>
+        <v>3:50</v>
       </c>
       <c r="H172" t="str">
-        <v>ZULAN</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L172" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Kissing The Ground</v>
+        <v>Joy</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G173" t="str">
-        <v>3:50</v>
+        <v>3:41</v>
       </c>
       <c r="H173" t="str">
-        <v>Nell Mescal</v>
+        <v>Dogstar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L173" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Joy</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>All In Now</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G174" t="str">
-        <v>3:41</v>
+        <v>2:44</v>
       </c>
       <c r="H174" t="str">
-        <v>Dogstar</v>
+        <v>Kany García</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L174" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Amor Bonito</v>
+        <v>Patchwork</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:44</v>
+        <v>3:07</v>
       </c>
       <c r="H175" t="str">
-        <v>Kany García</v>
+        <v>Carlita</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L175" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Patchwork</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Patchwork - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:07</v>
+        <v>3:24</v>
       </c>
       <c r="H176" t="str">
-        <v>Carlita</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L176" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>She's A Devil</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H177" t="str">
-        <v>Layton Giordani</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L177" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Do It All Alone</v>
+        <v>Time</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>3:20</v>
       </c>
       <c r="H178" t="str">
-        <v>Rend Collective</v>
+        <v>David Leonard</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L178" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Time</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Time - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:20</v>
+        <v>3:10</v>
       </c>
       <c r="H179" t="str">
-        <v>David Leonard</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L179" t="str">
-        <v>Time - David Leonard</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Andamos Ready</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H180" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L180" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Van y Vienen</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>3:46</v>
       </c>
       <c r="H181" t="str">
-        <v>El Fantasma</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L181" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>No Vuelvas</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:46</v>
+        <v>2:40</v>
       </c>
       <c r="H182" t="str">
-        <v>Majo Aguilar</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L182" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>RUNNIN</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:40</v>
+        <v>3:33</v>
       </c>
       <c r="H183" t="str">
-        <v>RUA YOUNG</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L183" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Talk You Through It</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G184" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H184" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L184" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Partners in Crime</v>
+        <v>Change your mind</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Born to Kill</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:50</v>
+        <v>3:21</v>
       </c>
       <c r="H185" t="str">
-        <v>Social Distortion</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L185" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Change your mind</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Change your mind - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:21</v>
+        <v>3:29</v>
       </c>
       <c r="H186" t="str">
-        <v>Casper Sage</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L186" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G187" t="str">
-        <v>3:29</v>
+        <v>3:17</v>
       </c>
       <c r="H187" t="str">
-        <v>The Franklin Electric</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L187" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Lover</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Train on the Island</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H188" t="str">
-        <v>Aldous Harding</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L188" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Lover</v>
+        <v>pink moon</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Lover - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H189" t="str">
-        <v>Juke Ross</v>
+        <v>runo plum</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L189" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>pink moon</v>
+        <v>Summer</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G190" t="str">
         <v>3:21</v>
       </c>
       <c r="H190" t="str">
-        <v>runo plum</v>
+        <v>Tasha</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L190" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Summer</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Summer - Single</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>4:20</v>
       </c>
       <c r="H191" t="str">
-        <v>Tasha</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L191" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Fabienk</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Vol.II</v>
       </c>
       <c r="G192" t="str">
-        <v>4:20</v>
+        <v>6:31</v>
       </c>
       <c r="H192" t="str">
-        <v>Nara's Room</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L192" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Fabienk</v>
+        <v>My Girl</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Vol.II</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>6:31</v>
+        <v>3:45</v>
       </c>
       <c r="H193" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Orca</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L193" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>My Girl</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Soren - EP</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:45</v>
+        <v>3:01</v>
       </c>
       <c r="H194" t="str">
-        <v>Orca</v>
+        <v>Dolder</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L194" t="str">
-        <v>My Girl - Orca</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Bone Structure</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:01</v>
+        <v>3:30</v>
       </c>
       <c r="H195" t="str">
-        <v>Dolder</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L195" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Turning Into Us</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:30</v>
+        <v>3:00</v>
       </c>
       <c r="H196" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Osé</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L196" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Fright</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-16</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:00</v>
+        <v>2:25</v>
       </c>
       <c r="H197" t="str">
-        <v>Osé</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L197" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Fright</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-16</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Fright - Single</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H198" t="str">
-        <v>Creepy Nuts</v>
+        <v>The Bends</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L198" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Smoking In Bed</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-16</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G199" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H199" t="str">
-        <v>The Bends</v>
+        <v>At The Gates</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L199" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>The Dissonant Void</v>
+        <v>Nine Days Of Rain</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-16</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G200" t="str">
-        <v>2:47</v>
+        <v>3:51</v>
       </c>
       <c r="H200" t="str">
-        <v>At The Gates</v>
+        <v>Melvins</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
       </c>
       <c r="L200" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Nine Days Of Rain - Melvins</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Invocation of the Dreamer</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D201" t="str">
         <v>2026-04-16</v>
@@ -8013,68 +8013,30 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Khemmis</v>
       </c>
       <c r="G201" t="str">
-        <v>3:51</v>
+        <v>4:46</v>
       </c>
       <c r="H201" t="str">
-        <v>Melvins</v>
+        <v>Khemmis</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
       <c r="L201" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Invocation of the Dreamer</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="G202" t="str">
-        <v>4:46</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
-      </c>
-      <c r="L202" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-16</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Mae Muller</v>
+        <v>Loreen</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-16</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Dead Pony</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-16</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-16</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>kenzie - where do we go</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-16</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>kenzie</v>
+        <v>Danna</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-16</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Foo Fighters</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-16</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Laufey</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-16</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Ella Langley</v>
+        <v>James Smith</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-16</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Mei Semones</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-16</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Evanescence</v>
+        <v>Ava Max</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-16</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>elijah woods</v>
+        <v>John Summit</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-16</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>colby!</v>
+        <v>Ava Max</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-16</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>The Chainsmokers</v>
+        <v>Danna</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-16</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>aron!</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-16</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Owen Riegling</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-16</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Laufey</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-16</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Teddy Swims</v>
+        <v>bleachers</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-16</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-16</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>LANY</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-16</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Sunday (1994)</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-16</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-16</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Freya Skye</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-16</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Bryan Adams</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-16</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>We Three</v>
+        <v>florencemachine</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-16</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Scorpions</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-16</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Bebe Rexha</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-16</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>The Lemon Twigs</v>
+        <v>HAUSER</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-16</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>METTE</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-16</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Saint Harison</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-16</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>NewDad</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-16</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Danna</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-16</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>florencemachine</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-16</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>HYBE LABELS</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-16</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Kungs</v>
+        <v>kenzie</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-16</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Charlie Puth</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-16</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Laufey</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-16</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-16</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Madison Cunningham</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-16</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Armin van Buuren</v>
+        <v>Evanescence</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-16</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>elijah woods</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-16</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Nothing But Thieves</v>
+        <v>colby!</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-16</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Ocean Alley</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-16</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>RAYE</v>
+        <v>aron!</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-16</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Take That</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-16</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Armik</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-16</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Switchfoot</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-16</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Peter Gabriel</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-16</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Sarah Julia</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-16</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Chris Norman</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-16</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Alan Walker</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-16</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Charlie Puth</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-16</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Miley Cyrus</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-16</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Conan Gray</v>
+        <v>We Three</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-16</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Charlie Puth</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-16</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Kylie Morgan</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-16</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-16</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Angelina Mango</v>
+        <v>METTE</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-16</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Julio Iglesias</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-16</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Loreen</v>
+        <v>NewDad</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-16</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Jessie Ware</v>
+        <v>Danna</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-16</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Holly Humberstone and Life is Strange</v>
+        <v>florencemachine</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone and Life is Strange</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B64" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-16</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-16</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Ella Langley</v>
+        <v>Kungs</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B66" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-16</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Eagles</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-16</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Moody Joody</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-16</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Jackson Dean</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B69" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-16</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-16</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Madison Cunningham</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-16</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>mary in the junkyard</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-16</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Adam Sanders</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=_p8eM5WzYbI</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-16</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>SIENNA SPIRO - The Visitor (Live from Blue Note Los Angeles) - SIENNA SPIRO</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>twocolors – Mad World (Official Video)</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=d6EOsQm455Q</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-16</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>twocolors</v>
+        <v>RAYE</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>twocolors – Mad World (Official Video) - twocolors</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=4dIWXI8VEdY</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-16</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>CamelPhat and 2 more</v>
+        <v>Take That</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>CamelPhat, Rafael Cerato - Don't Stop feat Amarha - CamelPhat and 2 more</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=PWsu9uma5SU</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-16</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Prince</v>
+        <v>Armik</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Prince - Lolita (Live at Club 3121, Las Vegas, January 20, 2007) - Prince</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=HtVcltkn3HI</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-16</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>RAYE</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>RAYE - 'Click Clack Symphony.' feat. Hans Zimmer (Official Video) - RAYE</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>The Warning - Kerosene (Performance Video)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=zaPVgMWYM3M</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-16</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>The Warning</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>The Warning - Kerosene (Performance Video) - The Warning</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=54-jKZ4ZdzA</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-16</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Pentatonix</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Pentatonix - Heaven On Earth (Official Video) - Pentatonix</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Xx5ESO5BHvU</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-16</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Tenille Townes</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Tenille Townes - we could use a little more (Music Video) - Tenille Townes</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=2Sn5X2Z5Img</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-16</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Jessie Ware</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Jessie Ware - Ride (GIDEÖN’s Darkroom Mix - Official Audio) - Jessie Ware</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=qBHLmQcLqhI</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-16</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Niall Horan</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Niall Horan - Dinner Party (Golden Hour Visual) - Niall Horan</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rubonkZnQ4g</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-16</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>John Summit and Major Lazer Official</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>John Summit - LIGHTS GO OUT (Major Lazer Remix) - John Summit and Major Lazer Official</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Stephen Stanley - Change (Official Video)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=i950RSL5cjY</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-16</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Stephen Stanley Music</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Stephen Stanley - Change (Official Video) - Stephen Stanley Music</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jackson Dean - Hey Mississippi</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=fFHn6_6Z6vQ</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-16</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Jackson Dean</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jackson Dean - Hey Mississippi - Jackson Dean</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=bBkMdkmtSU0</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-16</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Foo Fighters</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Foo Fighters - Caught In The Echo (Lyric Video) - Foo Fighters</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser)</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=WpSWuVBLeyY</v>
+        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-16</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ricky Martin and 2 more</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Dermot Kennedy - Honest (Official Visualiser) - Dermot Kennedy</v>
+        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer)</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=TMQ97CjRvTU</v>
+        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-16</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Billy Raffoul and Booshle G.</v>
+        <v>Angelina Mango</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Billy Raffoul &amp; Booshle G. w/ Tatum Tides - Honey (Official Visualizer) - Billy Raffoul and Booshle G.</v>
+        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video)</v>
+        <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=QemG9NDH2zI</v>
+        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-16</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Ella Langley</v>
+        <v>Julio Iglesias</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Ella Langley - Loving Life Again (Official Lyric Video) - Ella Langley</v>
+        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer)</v>
+        <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=9-yZpY9bilk</v>
+        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-16</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Cannons</v>
+        <v>Loreen</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Cannons - Light as a Feather (Official Visualizer) - Cannons</v>
+        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video)</v>
+        <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=2CWASL3F4bY</v>
+        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-16</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Luke Combs</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Luke Combs - The Way I Am (Official Studio Video) - Luke Combs</v>
+        <v>Jessie Ware - Automatic - Jessie Ware</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video]</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=mPFugXvNW1U</v>
+        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-16</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nessa Barrett</v>
+        <v>Holly Humberstone and Life is Strange</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nessa Barrett - Buffalo 66 (ft. Jesse Rutherford) [Official Music Video] - Nessa Barrett</v>
+        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone and Life is Strange</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Ugkk11NdZYI</v>
+        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-16</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>aron!</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>aron! - Wonderful Thing (Laundry Day) - aron!</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version)</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=WNOwEcNzCJw</v>
+        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-16</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Alessia Cara and Nelly Furtado</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Alessia Cara, Nelly Furtado - Shapeshifter (LOLT Version) - Alessia Cara and Nelly Furtado</v>
+        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DMA'S - My Baby's Place (Official Video)</v>
+        <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=IAw4zXa48vI</v>
+        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-16</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>DMA'S</v>
+        <v>Eagles</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>DMA'S - My Baby's Place (Official Video) - DMA'S</v>
+        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video)</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=_0DndLUSFYs</v>
+        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-16</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Moody Joody</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Thomas Anders ...sings Modern Talking - THE BEST IS YET TO COME (Official Video) - Thomas Anders TV and Modern Talking Offiziell</v>
+        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video)</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=IzBtROs4Ue8</v>
+        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-16</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (Official Lyric Video) - David Guetta and Jennifer Lopez</v>
+        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nick Carter - Love Life Tragedy</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=_kYRgEbOAiE</v>
+        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-16</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Nick Carter</v>
+        <v>John Summit and The Chainsmokers</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nick Carter - Love Life Tragedy - Nick Carter</v>
+        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video)</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=033viNHogN4</v>
+        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-16</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Carly Pearce</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Carly Pearce, Riley Green - If I Don't Leave I'm Gonna Stay (Lyric Video) - Carly Pearce</v>
+        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room</v>
+        <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=kZl-0EkxLUw</v>
+        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-16</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>OneRepublic</v>
+        <v>mary in the junkyard</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>OneRepublic - "Life In Color" | Live in Nova’s Red Room - OneRepublic</v>
+        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer)</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=R0tM45cPVpk</v>
+        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-16</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>4 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Jonas Blue and The Real Salif Keita</v>
+        <v>Adam Sanders</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Jonas Blue x Salif Keita Madan (Visualizer) - Jonas Blue and The Real Salif Keita</v>
+        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>BIAF &lt;3</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-16</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G102" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H102" t="str">
-        <v>Young Miko</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L102" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="103">
@@ -4654,13 +4654,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Sick Of Love</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-16</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>The Afterparty</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:36</v>
+        <v>2:50</v>
       </c>
       <c r="H113" t="str">
-        <v>Lykke Li</v>
+        <v>Young Miko</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L113" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>i just get worse</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-16</v>
@@ -4707,25 +4707,25 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>i just get worse - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G114" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H114" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L114" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="115">
@@ -4768,13 +4768,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Turnaround</v>
+        <v>i just get worse</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-16</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H116" t="str">
-        <v>54 Ultra</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L116" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Turnaround</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-16</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L117" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Madwoman</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-16</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:59</v>
+        <v>3:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Laufey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L118" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Madwoman</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-16</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G119" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H119" t="str">
-        <v>Hilary Duff</v>
+        <v>Laufey</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L119" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>One of Them</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-16</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>One of Them - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H120" t="str">
-        <v>DJ Khaled</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L120" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-16</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H121" t="str">
-        <v>Bossman Dlow</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L121" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>stuck</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-16</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>ghosted - EP</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G122" t="str">
-        <v>2:41</v>
+        <v>2:49</v>
       </c>
       <c r="H122" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L122" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>De Lejitos</v>
+        <v>stuck</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-16</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>De Lejitos - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H123" t="str">
-        <v>Jay Wheeler</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L123" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Echo</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-16</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Echo - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H124" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L124" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Where We Go</v>
+        <v>Echo</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-16</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Where We Go - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H125" t="str">
-        <v>Marshmello</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L125" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Where We Go</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-16</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Apambichao</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H126" t="str">
-        <v>Manuel Turizo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L126" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Of All People</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-16</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Apambichao</v>
       </c>
       <c r="G127" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H127" t="str">
-        <v>Foo Fighters</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L127" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Waves of You</v>
+        <v>Of All People</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-16</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Waves of You - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G128" t="str">
-        <v>3:15</v>
+        <v>2:34</v>
       </c>
       <c r="H128" t="str">
-        <v>After Hours</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L128" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-16</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H129" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L129" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-16</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L130" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-16</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G131" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L131" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-16</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H132" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L132" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-16</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H133" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L133" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-16</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>5:06</v>
+        <v>3:06</v>
       </c>
       <c r="H134" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L134" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-16</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G135" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H135" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L135" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-16</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G136" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H136" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L136" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-16</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G137" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H137" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L137" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-16</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L138" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Bubee</v>
+        <v>side slider</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-16</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Bubee - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G139" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H139" t="str">
-        <v>ILLIT</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L139" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Good Morning</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1893733064</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-16</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>24</v>
+        <v>SE9</v>
       </c>
       <c r="G140" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H140" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1893733056</v>
       </c>
       <c r="L140" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Positano</v>
+        <v>Bubee</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-16</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H141" t="str">
-        <v>Stephan Moccio</v>
+        <v>ILLIT</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L141" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>sophie</v>
+        <v>Good Morning</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-16</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>notes from the in between - EP</v>
+        <v>24</v>
       </c>
       <c r="G142" t="str">
-        <v>2:36</v>
+        <v>3:02</v>
       </c>
       <c r="H142" t="str">
-        <v>kenzie</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L142" t="str">
-        <v>sophie - kenzie</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>kiss goodbye</v>
+        <v>Positano</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-16</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G143" t="str">
-        <v>2:43</v>
+        <v>3:27</v>
       </c>
       <c r="H143" t="str">
-        <v>The Two Lips</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L143" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ENTRÉGAME</v>
+        <v>sophie</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-16</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H144" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>kenzie</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L144" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>EL SENTRITA</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-16</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>ETERNO</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:57</v>
+        <v>2:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Calle 24</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L145" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-16</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>DAWN PATROL</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G146" t="str">
-        <v>2:39</v>
+        <v>3:08</v>
       </c>
       <c r="H146" t="str">
-        <v>PARTY WAVE</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L146" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Formation</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-16</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Formation - Single</v>
+        <v>ETERNO</v>
       </c>
       <c r="G147" t="str">
-        <v>2:36</v>
+        <v>2:57</v>
       </c>
       <c r="H147" t="str">
-        <v>Adekunle Gold</v>
+        <v>Calle 24</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L147" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Who Will You Follow</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-16</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Sanctuary</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G148" t="str">
-        <v>3:55</v>
+        <v>2:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Evanescence</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L148" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>That's When You Know</v>
+        <v>Formation</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-16</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:13</v>
+        <v>2:36</v>
       </c>
       <c r="H149" t="str">
-        <v>Kygo</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L149" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drinking Game</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-16</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Drinking Game - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G150" t="str">
-        <v>2:50</v>
+        <v>3:55</v>
       </c>
       <c r="H150" t="str">
-        <v>Warren Zeiders</v>
+        <v>Evanescence</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L150" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Anything But Me</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-16</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>In The Feeling</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>4:59</v>
+        <v>3:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Owen Riegling</v>
+        <v>Kygo</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L151" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>American Dream</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-16</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>American Dream - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H152" t="str">
-        <v>Alabama Shakes</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L152" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Already There</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-16</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Victory Garden</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G153" t="str">
-        <v>3:50</v>
+        <v>4:59</v>
       </c>
       <c r="H153" t="str">
-        <v>Young the Giant</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L153" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>American Dream</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-16</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>KINDA HARD</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:47</v>
+        <v>4:27</v>
       </c>
       <c r="H154" t="str">
-        <v>Bilmuri</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L154" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Alone For A Year</v>
+        <v>Already There</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-16</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Joy Next Door</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G155" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H155" t="str">
-        <v>The Maine</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L155" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Bring Home My Man</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-16</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G156" t="str">
-        <v>4:22</v>
+        <v>2:47</v>
       </c>
       <c r="H156" t="str">
-        <v>Maya Hawke</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L156" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SUPERMAN</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-16</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G157" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H157" t="str">
-        <v>South Arcade</v>
+        <v>The Maine</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L157" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>1989</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-16</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>1989 - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G158" t="str">
-        <v>2:34</v>
+        <v>4:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Nightly</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L158" t="str">
-        <v>1989 - Nightly</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>waste your pain</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-16</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>waste your pain - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:23</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Cruz Beckham</v>
+        <v>South Arcade</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L159" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Strangers</v>
+        <v>1989</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-16</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H160" t="str">
-        <v>Tink</v>
+        <v>Nightly</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L160" t="str">
-        <v>Strangers - Tink</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Right In Front Of Me</v>
+        <v>waste your pain</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-16</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:45</v>
+        <v>2:23</v>
       </c>
       <c r="H161" t="str">
-        <v>Tiny Habits</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L161" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SAME SH!T</v>
+        <v>Strangers</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-16</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G162" t="str">
-        <v>3:13</v>
+        <v>2:44</v>
       </c>
       <c r="H162" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tink</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L162" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-16</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>The End is Not the End</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:12</v>
+        <v>2:45</v>
       </c>
       <c r="H163" t="str">
-        <v>Atreyu</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L163" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Heal</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-16</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Heal - Single</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H164" t="str">
-        <v>HAYLA</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L164" t="str">
-        <v>Heal - HAYLA</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Free</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-16</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G165" t="str">
-        <v>4:13</v>
+        <v>4:12</v>
       </c>
       <c r="H165" t="str">
-        <v>Simone Ashley</v>
+        <v>Atreyu</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L165" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cállate</v>
+        <v>Heal</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-16</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:59</v>
+        <v>3:26</v>
       </c>
       <c r="H166" t="str">
-        <v>Dua Saleh</v>
+        <v>HAYLA</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L166" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Raindrops</v>
+        <v>Free</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-16</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Raindrops - Single</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>3:34</v>
+        <v>4:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Rick Astley</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L167" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>WORK OF ART</v>
+        <v>Cállate</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-16</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>PRODIGY</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G168" t="str">
-        <v>2:27</v>
+        <v>1:59</v>
       </c>
       <c r="H168" t="str">
-        <v>Tkandz</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L168" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Scottie Pippen</v>
+        <v>Raindrops</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-16</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:34</v>
+        <v>3:34</v>
       </c>
       <c r="H169" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L169" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Damn Good Actress</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-16</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G170" t="str">
-        <v>2:49</v>
+        <v>2:27</v>
       </c>
       <c r="H170" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Tkandz</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L170" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Ricota</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-16</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Ricota - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:25</v>
+        <v>2:34</v>
       </c>
       <c r="H171" t="str">
-        <v>ZULAN</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L171" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Kissing The Ground</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-16</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:50</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>Nell Mescal</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L172" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Joy</v>
+        <v>Ricota</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-16</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>All In Now</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H173" t="str">
-        <v>Dogstar</v>
+        <v>ZULAN</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L173" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Amor Bonito</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-16</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H174" t="str">
-        <v>Kany García</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L174" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Patchwork</v>
+        <v>Joy</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-16</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Patchwork - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G175" t="str">
-        <v>3:07</v>
+        <v>3:41</v>
       </c>
       <c r="H175" t="str">
-        <v>Carlita</v>
+        <v>Dogstar</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L175" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>She's A Devil</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-16</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>She's A Devil - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G176" t="str">
-        <v>3:24</v>
+        <v>2:44</v>
       </c>
       <c r="H176" t="str">
-        <v>Layton Giordani</v>
+        <v>Kany García</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L176" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Do It All Alone</v>
+        <v>Patchwork</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-16</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H177" t="str">
-        <v>Rend Collective</v>
+        <v>Carlita</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L177" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Time</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-16</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Time - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H178" t="str">
-        <v>David Leonard</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L178" t="str">
-        <v>Time - David Leonard</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Andamos Ready</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-16</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:10</v>
+        <v>2:52</v>
       </c>
       <c r="H179" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L179" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Van y Vienen</v>
+        <v>Time</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-16</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H180" t="str">
-        <v>El Fantasma</v>
+        <v>David Leonard</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L180" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>No Vuelvas</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-16</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H181" t="str">
-        <v>Majo Aguilar</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L181" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>RUNNIN</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-16</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>RUA YOUNG</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L182" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Talk You Through It</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-16</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:33</v>
+        <v>3:46</v>
       </c>
       <c r="H183" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L183" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Partners in Crime</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-16</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Born to Kill</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H184" t="str">
-        <v>Social Distortion</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L184" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Change your mind</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-16</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Change your mind - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H185" t="str">
-        <v>Casper Sage</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L185" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-16</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G186" t="str">
-        <v>3:29</v>
+        <v>3:50</v>
       </c>
       <c r="H186" t="str">
-        <v>The Franklin Electric</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L186" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Change your mind</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-16</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Train on the Island</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H187" t="str">
-        <v>Aldous Harding</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L187" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Lover</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-16</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Lover - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H188" t="str">
-        <v>Juke Ross</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L188" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>pink moon</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-16</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G189" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H189" t="str">
-        <v>runo plum</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L189" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Summer</v>
+        <v>Lover</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-16</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Summer - Single</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H190" t="str">
-        <v>Tasha</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L190" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Lizzie mcguire</v>
+        <v>pink moon</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-16</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G191" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H191" t="str">
-        <v>Nara's Room</v>
+        <v>runo plum</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L191" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Fabienk</v>
+        <v>Summer</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-16</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Vol.II</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>6:31</v>
+        <v>3:21</v>
       </c>
       <c r="H192" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Tasha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L192" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>My Girl</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-16</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Soren - EP</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>4:20</v>
       </c>
       <c r="H193" t="str">
-        <v>Orca</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L193" t="str">
-        <v>My Girl - Orca</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Bone Structure</v>
+        <v>Fabienk</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-16</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Vol.II</v>
       </c>
       <c r="G194" t="str">
-        <v>3:01</v>
+        <v>6:31</v>
       </c>
       <c r="H194" t="str">
-        <v>Dolder</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L194" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Turning Into Us</v>
+        <v>My Girl</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-16</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H195" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Orca</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L195" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-16</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:00</v>
+        <v>3:01</v>
       </c>
       <c r="H196" t="str">
-        <v>Osé</v>
+        <v>Dolder</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L196" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Fright</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-16</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Fright - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H197" t="str">
-        <v>Creepy Nuts</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L197" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Smoking In Bed</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-16</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H198" t="str">
-        <v>The Bends</v>
+        <v>Osé</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L198" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>The Dissonant Void</v>
+        <v>Fright</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-16</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:47</v>
+        <v>2:25</v>
       </c>
       <c r="H199" t="str">
-        <v>At The Gates</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L199" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-16</v>
@@ -7975,68 +7975,144 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:51</v>
+        <v>3:24</v>
       </c>
       <c r="H200" t="str">
-        <v>Melvins</v>
+        <v>The Bends</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L200" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>The Dissonant Void</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H201" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+      </c>
+      <c r="L201" t="str">
+        <v>The Dissonant Void - At The Gates</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D203" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G203" t="str">
         <v>4:46</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H203" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K203" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L203" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>6 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 hours ago</v>
+        <v>10h ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,19 +439,19 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>8h ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8h ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8h ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8h ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>10h ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B88" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4236,3883 +4236,3769 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>drop dead</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>The Nightlife</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G102" t="str">
-        <v>3:32</v>
+        <v>3:44</v>
       </c>
       <c r="H102" t="str">
-        <v>Honey Dijon</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L102" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>First Light</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H103" t="str">
-        <v>DANNA</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L103" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Bottom Of Your Boots</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Dandelion</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G104" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H104" t="str">
-        <v>Ella Langley</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L104" t="str">
-        <v>Bottom Of Your Boots - Ella Langley</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>RUNWAY</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/runway/1891472591</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>RUNWAY - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G105" t="str">
-        <v>2:51</v>
+        <v>2:36</v>
       </c>
       <c r="H105" t="str">
-        <v>Lady Gaga</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/runway/1891472590</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L105" t="str">
-        <v>RUNWAY - Lady Gaga</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Back and Forth (feat. Missy Elliott)</v>
+        <v>Rackies</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Kehlani</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G106" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H106" t="str">
-        <v>Kehlani</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L106" t="str">
-        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mr. Know It All</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Mr. Know It All - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H107" t="str">
-        <v>Teddy Swims</v>
+        <v>Tyla</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L107" t="str">
-        <v>Mr. Know It All - Teddy Swims</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Bad Angel</v>
+        <v>Potential</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Bad Angel - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>2:33</v>
+        <v>4:02</v>
       </c>
       <c r="H108" t="str">
-        <v>Anyma</v>
+        <v>sombr</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L108" t="str">
-        <v>Bad Angel - Anyma</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Step (feat. Swizz Beatz)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>10 Til' Midnight</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H109" t="str">
-        <v>Snoop Dogg</v>
+        <v>Maluma</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L109" t="str">
-        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Sweet Hallelujah</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Sweet Hallelujah - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G110" t="str">
-        <v>3:02</v>
+        <v>3:32</v>
       </c>
       <c r="H110" t="str">
-        <v>Royel Otis</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L110" t="str">
-        <v>Sweet Hallelujah - Royel Otis</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Beauty Pageant</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Cruel World</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:15</v>
+        <v>2:50</v>
       </c>
       <c r="H111" t="str">
-        <v>Holly Humberstone</v>
+        <v>Young Miko</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L111" t="str">
-        <v>Beauty Pageant - Holly Humberstone</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PINKY UP</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>PINKY UP - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>2:11</v>
+        <v>3:14</v>
       </c>
       <c r="H112" t="str">
-        <v>KATSEYE</v>
+        <v>DANNA</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L112" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>BIAF &lt;3</v>
+        <v>i just get worse</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H113" t="str">
-        <v>Young Miko</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L113" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Sick Of Love</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>The Afterparty</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G114" t="str">
-        <v>3:36</v>
+        <v>3:23</v>
       </c>
       <c r="H114" t="str">
-        <v>Lykke Li</v>
+        <v>John Summit</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L114" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Ember</v>
+        <v>Side Effects</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G115" t="str">
-        <v>3:25</v>
+        <v>3:17</v>
       </c>
       <c r="H115" t="str">
-        <v>Iceage</v>
+        <v>ZAYN</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L115" t="str">
-        <v>Ember - Iceage</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>i just get worse</v>
+        <v>Numb</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>i just get worse - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Kevian Kraemer</v>
+        <v>JT</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L116" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Turnaround</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:14</v>
+        <v>3:05</v>
       </c>
       <c r="H117" t="str">
-        <v>54 Ultra</v>
+        <v>Labrinth</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L117" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:05</v>
+        <v>2:47</v>
       </c>
       <c r="H118" t="str">
-        <v>Labrinth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L118" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Madwoman</v>
+        <v>My Way</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:59</v>
+        <v>4:02</v>
       </c>
       <c r="H119" t="str">
-        <v>Laufey</v>
+        <v>Riley Green</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L119" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Ache</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:33</v>
+        <v>4:25</v>
       </c>
       <c r="H120" t="str">
-        <v>Hilary Duff</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L120" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>One of Them</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>One of Them - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G121" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H121" t="str">
-        <v>DJ Khaled</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L121" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:49</v>
+        <v>2:13</v>
       </c>
       <c r="H122" t="str">
-        <v>Bossman Dlow</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L122" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>stuck</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>ghosted - EP</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G123" t="str">
-        <v>2:41</v>
+        <v>3:57</v>
       </c>
       <c r="H123" t="str">
-        <v>Saint Harison</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L123" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>De Lejitos</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>De Lejitos - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:27</v>
+        <v>4:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Jay Wheeler</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L124" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Echo</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Echo - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:39</v>
+        <v>3:26</v>
       </c>
       <c r="H125" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L125" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Where We Go</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Where We Go - Single</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:16</v>
+        <v>2:22</v>
       </c>
       <c r="H126" t="str">
-        <v>Marshmello</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L126" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Apambichao</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G127" t="str">
-        <v>2:41</v>
+        <v>2:34</v>
       </c>
       <c r="H127" t="str">
-        <v>Manuel Turizo</v>
+        <v>MUNA</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L127" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Of All People</v>
+        <v>Superbloom</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Superbloom</v>
       </c>
       <c r="G128" t="str">
-        <v>2:34</v>
+        <v>4:11</v>
       </c>
       <c r="H128" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L128" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Waves of You</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Waves of You - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:15</v>
+        <v>1:40</v>
       </c>
       <c r="H129" t="str">
-        <v>After Hours</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L129" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>idea 1</v>
+        <v>Make You Move</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>idea 1 - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>2:24</v>
       </c>
       <c r="H130" t="str">
-        <v>Kelela</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L130" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Attitude</v>
+        <v>FERRARI</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Sweat</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:13</v>
+        <v>2:14</v>
       </c>
       <c r="H131" t="str">
-        <v>Melanie C</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L131" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Stick With You</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G132" t="str">
-        <v>2:54</v>
+        <v>2:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Kylie Cantrall</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L132" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Work</v>
+        <v>KGB</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Work - Single</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H133" t="str">
-        <v>Pitbull</v>
+        <v>Adela</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/adela/1423152831</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L133" t="str">
-        <v>Work - Pitbull</v>
+        <v>KGB - Adela</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Obvious</v>
+        <v>Holly!</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Obvious - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:06</v>
+        <v>3:10</v>
       </c>
       <c r="H134" t="str">
-        <v>Chris Brown</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L134" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>As Time Goes By</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>CINEMATIC</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G135" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H135" t="str">
-        <v>Josh Groban</v>
+        <v>6LACK</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L135" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>My Mess</v>
+        <v>Move Time</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H136" t="str">
-        <v>Myles Smith</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L136" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Going Shopping</v>
+        <v>I Want You</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Reality Awaits</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G137" t="str">
-        <v>4:21</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>The Strokes</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L137" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Choka Choka</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:11</v>
+        <v>3:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Anitta</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L138" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>side slider</v>
+        <v>Ring</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:47</v>
+        <v>3:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Isaia Huron</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L139" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Woman I Am</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1893733064</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>SE9</v>
+        <v>Wild</v>
       </c>
       <c r="G140" t="str">
-        <v>3:31</v>
+        <v>3:24</v>
       </c>
       <c r="H140" t="str">
-        <v>Skye Newman</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1893733056</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L140" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Bubee</v>
+        <v>Stay Love</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Bubee - Single</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G141" t="str">
-        <v>3:02</v>
+        <v>3:26</v>
       </c>
       <c r="H141" t="str">
-        <v>ILLIT</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L141" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Good Morning</v>
+        <v>Love Me</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>24</v>
+        <v>Dear God</v>
       </c>
       <c r="G142" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H142" t="str">
-        <v>Alexis Ffrench</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L142" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Positano</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H143" t="str">
-        <v>Stephan Moccio</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L143" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>sophie</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G144" t="str">
-        <v>2:36</v>
+        <v>3:52</v>
       </c>
       <c r="H144" t="str">
-        <v>kenzie</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L144" t="str">
-        <v>sophie - kenzie</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>kiss goodbye</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:43</v>
+        <v>3:08</v>
       </c>
       <c r="H145" t="str">
-        <v>The Two Lips</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L145" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ENTRÉGAME</v>
+        <v>Desgraça</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G146" t="str">
-        <v>3:08</v>
+        <v>2:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>Anitta</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L146" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>EL SENTRITA</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>ETERNO</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G147" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H147" t="str">
-        <v>Calle 24</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L147" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>Dansons</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>DAWN PATROL</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:39</v>
+        <v>3:26</v>
       </c>
       <c r="H148" t="str">
-        <v>PARTY WAVE</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L148" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Formation</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Formation - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:36</v>
+        <v>2:57</v>
       </c>
       <c r="H149" t="str">
-        <v>Adekunle Gold</v>
+        <v>Trousdale</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L149" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Who Will You Follow</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Sanctuary</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G150" t="str">
-        <v>3:55</v>
+        <v>5:21</v>
       </c>
       <c r="H150" t="str">
-        <v>Evanescence</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L150" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>That's When You Know</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>That's When You Know - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G151" t="str">
-        <v>3:13</v>
+        <v>2:49</v>
       </c>
       <c r="H151" t="str">
-        <v>Kygo</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L151" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drinking Game</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Drinking Game - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G152" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H152" t="str">
-        <v>Warren Zeiders</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L152" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Anything But Me</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>In The Feeling</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G153" t="str">
-        <v>4:59</v>
+        <v>7:56</v>
       </c>
       <c r="H153" t="str">
-        <v>Owen Riegling</v>
+        <v>TOMORA</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L153" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>American Dream</v>
+        <v>Everything U</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>American Dream - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G154" t="str">
-        <v>4:27</v>
+        <v>3:30</v>
       </c>
       <c r="H154" t="str">
-        <v>Alabama Shakes</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L154" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Already There</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Victory Garden</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:50</v>
+        <v>4:21</v>
       </c>
       <c r="H155" t="str">
-        <v>Young the Giant</v>
+        <v>ZERB</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L155" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>KINDA HARD</v>
+        <v>soft pop</v>
       </c>
       <c r="G156" t="str">
-        <v>2:47</v>
+        <v>3:02</v>
       </c>
       <c r="H156" t="str">
-        <v>Bilmuri</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L156" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Alone For A Year</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Joy Next Door</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H157" t="str">
-        <v>The Maine</v>
+        <v>Subtronics</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L157" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Bring Home My Man</v>
+        <v>Track 3</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/track-3/1889992071</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G158" t="str">
-        <v>4:22</v>
+        <v>2:56</v>
       </c>
       <c r="H158" t="str">
-        <v>Maya Hawke</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/track-3/1889992065</v>
       </c>
       <c r="L158" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Track 3 - rjtheweirdo</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SUPERMAN</v>
+        <v>Outside</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H159" t="str">
-        <v>South Arcade</v>
+        <v>Inayah</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L159" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>1989</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>1989 - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:34</v>
+        <v>2:25</v>
       </c>
       <c r="H160" t="str">
-        <v>Nightly</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L160" t="str">
-        <v>1989 - Nightly</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>waste your pain</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>waste your pain - Single</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H161" t="str">
-        <v>Cruz Beckham</v>
+        <v>Max McNown</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L161" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Strangers</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G162" t="str">
-        <v>2:44</v>
+        <v>4:19</v>
       </c>
       <c r="H162" t="str">
-        <v>Tink</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L162" t="str">
-        <v>Strangers - Tink</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:45</v>
+        <v>3:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Tiny Habits</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L163" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SAME SH!T</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H164" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L164" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Deep Water</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>The End is Not the End</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G165" t="str">
-        <v>4:12</v>
+        <v>2:33</v>
       </c>
       <c r="H165" t="str">
-        <v>Atreyu</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L165" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Heal</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Heal - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G166" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H166" t="str">
-        <v>HAYLA</v>
+        <v>ERNEST</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L166" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Free</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:13</v>
+        <v>1:58</v>
       </c>
       <c r="H167" t="str">
-        <v>Simone Ashley</v>
+        <v>Marca MP</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L167" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cállate</v>
+        <v>Price of Love</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>1:59</v>
+        <v>3:29</v>
       </c>
       <c r="H168" t="str">
-        <v>Dua Saleh</v>
+        <v>Benny G</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L168" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Raindrops</v>
+        <v>Las Flores</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Raindrops - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:34</v>
+        <v>2:59</v>
       </c>
       <c r="H169" t="str">
-        <v>Rick Astley</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L169" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>WORK OF ART</v>
+        <v>To The Moon</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>PRODIGY</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:27</v>
+        <v>3:42</v>
       </c>
       <c r="H170" t="str">
-        <v>Tkandz</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L170" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Scottie Pippen</v>
+        <v>MATCHA</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G171" t="str">
-        <v>2:34</v>
+        <v>2:36</v>
       </c>
       <c r="H171" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L171" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Damn Good Actress</v>
+        <v>PROWLER</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>2:45</v>
       </c>
       <c r="H172" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Waterparks</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L172" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ricota</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ricota - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:25</v>
+        <v>3:14</v>
       </c>
       <c r="H173" t="str">
-        <v>ZULAN</v>
+        <v>Wage War</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L173" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Kissing The Ground</v>
+        <v>how far down</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G174" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H174" t="str">
-        <v>Nell Mescal</v>
+        <v>Camylio</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L174" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Joy</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>All In Now</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:41</v>
+        <v>2:26</v>
       </c>
       <c r="H175" t="str">
-        <v>Dogstar</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L175" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Amor Bonito</v>
+        <v>Spin</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:44</v>
+        <v>4:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Kany García</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L176" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Patchwork</v>
+        <v>MILAN</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Patchwork - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:07</v>
+        <v>2:16</v>
       </c>
       <c r="H177" t="str">
-        <v>Carlita</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L177" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>She's A Devil</v>
+        <v>SHABA</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>She's A Devil - Single</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:01</v>
       </c>
       <c r="H178" t="str">
-        <v>Layton Giordani</v>
+        <v>SPINALL</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L178" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Do It All Alone</v>
+        <v>Forever</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G179" t="str">
-        <v>2:52</v>
+        <v>3:38</v>
       </c>
       <c r="H179" t="str">
-        <v>Rend Collective</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L179" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Time</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Time - Single</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:20</v>
+        <v>2:46</v>
       </c>
       <c r="H180" t="str">
-        <v>David Leonard</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L180" t="str">
-        <v>Time - David Leonard</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Andamos Ready</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G181" t="str">
-        <v>3:10</v>
+        <v>2:57</v>
       </c>
       <c r="H181" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Terror</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L181" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Van y Vienen</v>
+        <v>Confused</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G182" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H182" t="str">
-        <v>El Fantasma</v>
+        <v>cortex</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L182" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No Vuelvas</v>
+        <v>On The Low</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:46</v>
+        <v>3:29</v>
       </c>
       <c r="H183" t="str">
-        <v>Majo Aguilar</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L183" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>RUNNIN</v>
+        <v>Wannabe</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:40</v>
+        <v>2:30</v>
       </c>
       <c r="H184" t="str">
-        <v>RUA YOUNG</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L184" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Talk You Through It</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>Middle Child</v>
       </c>
       <c r="G185" t="str">
-        <v>3:33</v>
+        <v>3:32</v>
       </c>
       <c r="H185" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Amma</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L185" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Partners in Crime</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Born to Kill</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G186" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H186" t="str">
-        <v>Social Distortion</v>
+        <v>Venom</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L186" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Change your mind</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Change your mind - Single</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:21</v>
+        <v>3:22</v>
       </c>
       <c r="H187" t="str">
-        <v>Casper Sage</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L187" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Taylor</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G188" t="str">
-        <v>3:29</v>
+        <v>4:15</v>
       </c>
       <c r="H188" t="str">
-        <v>The Franklin Electric</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L188" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Yours</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Train on the Island</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:17</v>
+        <v>4:26</v>
       </c>
       <c r="H189" t="str">
-        <v>Aldous Harding</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L189" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Lover</v>
+        <v>Pepper</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Lover - Single</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:26</v>
+        <v>4:54</v>
       </c>
       <c r="H190" t="str">
-        <v>Juke Ross</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L190" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>pink moon</v>
+        <v>No Driver</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Roses</v>
       </c>
       <c r="G191" t="str">
-        <v>3:21</v>
+        <v>3:48</v>
       </c>
       <c r="H191" t="str">
-        <v>runo plum</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L191" t="str">
-        <v>pink moon - runo plum</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Summer</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Summer - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H192" t="str">
-        <v>Tasha</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L192" t="str">
-        <v>Summer - Tasha</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Lizzie mcguire</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:20</v>
+        <v>2:18</v>
       </c>
       <c r="H193" t="str">
-        <v>Nara's Room</v>
+        <v>H.LLS</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L193" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Fabienk</v>
+        <v>Powder</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Vol.II</v>
+        <v>Powder</v>
       </c>
       <c r="G194" t="str">
-        <v>6:31</v>
+        <v>4:41</v>
       </c>
       <c r="H194" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L194" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>My Girl</v>
+        <v>Knuckle</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Soren - EP</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:45</v>
+        <v>2:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Orca</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L195" t="str">
-        <v>My Girl - Orca</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Bone Structure</v>
+        <v>For The Ride</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Bone Structure - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:01</v>
+        <v>2:43</v>
       </c>
       <c r="H196" t="str">
-        <v>Dolder</v>
+        <v>Snakehips</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L196" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Turning Into Us</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:30</v>
+        <v>2:19</v>
       </c>
       <c r="H197" t="str">
-        <v>Rhys Rutherford</v>
+        <v>daydreamers</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L197" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>WYD</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:00</v>
+        <v>2:36</v>
       </c>
       <c r="H198" t="str">
-        <v>Osé</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L198" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Fright</v>
+        <v>Dig Your Own Grave</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Fright - Single</v>
+        <v>Strike and Kill</v>
       </c>
       <c r="G199" t="str">
-        <v>2:25</v>
+        <v>4:29</v>
       </c>
       <c r="H199" t="str">
-        <v>Creepy Nuts</v>
+        <v>DevilDriver</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
       </c>
       <c r="L199" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Dig Your Own Grave - DevilDriver</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Smoking In Bed</v>
+        <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>The Dead Ones</v>
       </c>
       <c r="G200" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H200" t="str">
-        <v>The Bends</v>
+        <v>The Last Ten Seconds of Life</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
       <c r="L200" t="str">
-        <v>Smoking In Bed - The Bends</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>The Dissonant Void</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>The Ghost of a Future Dead</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H201" t="str">
-        <v>At The Gates</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
-      </c>
-      <c r="L201" t="str">
-        <v>The Dissonant Void - At The Gates</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Nine Days Of Rain</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G202" t="str">
-        <v>3:51</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Invocation of the Dreamer</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="G203" t="str">
-        <v>4:46</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Invocation of the Dreamer - Khemmis</v>
+        <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>13 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>13 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>13 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -5435,19 +5435,19 @@
         <v>2:37</v>
       </c>
       <c r="H133" t="str">
-        <v>Adela</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/adela/1423152831</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K133" t="str">
         <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L133" t="str">
-        <v>KGB - Adela</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="134">
@@ -6364,13 +6364,13 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Track 3</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/track-3/1889992071</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-17</v>
@@ -6394,10 +6394,10 @@
         <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/track-3/1889992065</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L158" t="str">
-        <v>Track 3 - rjtheweirdo</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="159">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B54" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B61" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B66" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B69" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B76" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B78" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B82" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B83" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B85" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
       </c>
       <c r="B88" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Julio Iglesias - Nathalie (Nathalie)</v>
       </c>
       <c r="B89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Loreen - Coming Close (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Jessie Ware - Automatic</v>
       </c>
       <c r="B91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Eagles - One Of These Nights (Official Audio)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Moody Joody - Loretta's Last Call (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>mary in the junkyard - Crash Landing (Official)</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2263,7 +2263,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -5376,13 +5376,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-17</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H132" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L132" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-17</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G133" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H133" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L133" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-17</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H134" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L134" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-17</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H135" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L135" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-17</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G136" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H136" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L136" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-17</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H137" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L137" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-17</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G138" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H138" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L138" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-17</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H139" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L139" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-17</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H140" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L140" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-17</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G141" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H141" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L141" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-17</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G142" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H142" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L142" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-17</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G143" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H143" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L143" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-17</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H144" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L144" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-17</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G145" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H145" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L145" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-17</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H146" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L146" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-17</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G147" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H147" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L147" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-17</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G148" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H148" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L148" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-17</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H149" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L149" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-17</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H150" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L150" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-17</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H151" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L151" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-17</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H152" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L152" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-17</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G153" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H153" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L153" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-17</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G154" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H154" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L154" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-17</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G155" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H155" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L155" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-17</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H156" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L156" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-17</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G157" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H157" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L157" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-17</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H158" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L158" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-17</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G159" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H159" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L159" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-17</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H160" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L160" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-17</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L161" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-17</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H162" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L162" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-17</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G163" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H163" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L163" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-17</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H164" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L164" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-17</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H165" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L165" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-17</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G166" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H166" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L166" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-17</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G167" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H167" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L167" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-17</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H168" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L168" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-17</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H169" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L169" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-17</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H170" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L170" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-17</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H171" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L171" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-17</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G172" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H172" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L172" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-17</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H173" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L173" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-17</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L174" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-17</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G175" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H175" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L175" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-17</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H176" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L176" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-17</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H177" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L177" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-17</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H178" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L178" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-17</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H179" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L179" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-17</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G180" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H180" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L180" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-17</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L181" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-17</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G182" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H182" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L182" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-17</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G183" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H183" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L183" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-17</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H184" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L184" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-17</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H185" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L185" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-17</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G186" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H186" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L186" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-17</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G187" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H187" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L187" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-17</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H188" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L188" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-17</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G189" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H189" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L189" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-17</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H190" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L190" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-17</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H191" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L191" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-17</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G192" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H192" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L192" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-17</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H193" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L193" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-17</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H194" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L194" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-17</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G195" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H195" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L195" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-17</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L196" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-17</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H197" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L197" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-17</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H198" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L198" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-17</v>
@@ -7937,68 +7937,106 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H199" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L199" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G200" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H200" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D201" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G201" t="str">
         <v>3:32</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H201" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L201" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -1275,7 +1275,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E201" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -819,7 +819,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1123,7 +1123,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>First Light</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D103" t="str">
         <v>2026-04-18</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>First Light - Single</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G103" t="str">
-        <v>3:24</v>
+        <v>5:03</v>
       </c>
       <c r="H103" t="str">
-        <v>Lana Del Rey</v>
+        <v>Madonna</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L103" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Focu 'Ranni</v>
+        <v>First Light</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D104" t="str">
         <v>2026-04-18</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:50</v>
+        <v>3:24</v>
       </c>
       <c r="H104" t="str">
-        <v>ROSALÍA</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L104" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D105" t="str">
         <v>2026-04-18</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Middle of Nowhere</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G105" t="str">
-        <v>2:36</v>
+        <v>2:50</v>
       </c>
       <c r="H105" t="str">
-        <v>Kacey Musgraves</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L105" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Rackies</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D106" t="str">
         <v>2026-04-18</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G106" t="str">
-        <v>2:53</v>
+        <v>2:36</v>
       </c>
       <c r="H106" t="str">
-        <v>Sexyy Red</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L106" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>Rackies</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D107" t="str">
         <v>2026-04-18</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G107" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H107" t="str">
-        <v>Tyla</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L107" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Potential</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D108" t="str">
         <v>2026-04-18</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Potential - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>4:02</v>
+        <v>3:33</v>
       </c>
       <c r="H108" t="str">
-        <v>sombr</v>
+        <v>Tyla</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L108" t="str">
-        <v>Potential - sombr</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pa' la seca</v>
+        <v>Potential</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D109" t="str">
         <v>2026-04-18</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:04</v>
+        <v>4:02</v>
       </c>
       <c r="H109" t="str">
-        <v>Maluma</v>
+        <v>sombr</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L109" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D110" t="str">
         <v>2026-04-18</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>The Nightlife</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H110" t="str">
-        <v>Honey Dijon</v>
+        <v>Maluma</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L110" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>BIAF &lt;3</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D111" t="str">
         <v>2026-04-18</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G111" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H111" t="str">
-        <v>Young Miko</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L111" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D112" t="str">
         <v>2026-04-18</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H112" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L112" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>i just get worse</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D113" t="str">
         <v>2026-04-18</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>i just get worse - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H113" t="str">
-        <v>Kevian Kraemer</v>
+        <v>DANNA</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L113" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>i just get worse</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D114" t="str">
         <v>2026-04-18</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H114" t="str">
-        <v>John Summit</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L114" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Side Effects</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D115" t="str">
         <v>2026-04-18</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>KONNAKOL</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G115" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H115" t="str">
-        <v>ZAYN</v>
+        <v>John Summit</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L115" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Numb</v>
+        <v>Side Effects</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D116" t="str">
         <v>2026-04-18</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Numb - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G116" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>JT</v>
+        <v>ZAYN</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L116" t="str">
-        <v>Numb - JT</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Numb</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D117" t="str">
         <v>2026-04-18</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>JT</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L117" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D118" t="str">
         <v>2026-04-18</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H118" t="str">
-        <v>Miley Cyrus</v>
+        <v>Labrinth</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L118" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>My Way</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D119" t="str">
         <v>2026-04-18</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>My Way - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>4:02</v>
+        <v>2:47</v>
       </c>
       <c r="H119" t="str">
-        <v>Riley Green</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L119" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Ache</v>
+        <v>My Way</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D120" t="str">
         <v>2026-04-18</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Bloom - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H120" t="str">
-        <v>Not for Radio</v>
+        <v>Riley Green</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L120" t="str">
-        <v>Ache - Not for Radio</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Cut Ties</v>
+        <v>Ache</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D121" t="str">
         <v>2026-04-18</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:09</v>
+        <v>4:25</v>
       </c>
       <c r="H121" t="str">
-        <v>Anne Hathaway</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L121" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D122" t="str">
         <v>2026-04-18</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G122" t="str">
-        <v>2:13</v>
+        <v>4:09</v>
       </c>
       <c r="H122" t="str">
-        <v>Slayyyter</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L122" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D123" t="str">
         <v>2026-04-18</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Nine Inch Noize</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:57</v>
+        <v>2:13</v>
       </c>
       <c r="H123" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L123" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Boots on the Ground</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D124" t="str">
         <v>2026-04-18</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G124" t="str">
-        <v>4:21</v>
+        <v>3:57</v>
       </c>
       <c r="H124" t="str">
-        <v>Massive Attack</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L124" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D125" t="str">
         <v>2026-04-18</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H125" t="str">
-        <v>Demi Lovato</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L125" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>I CONDEMN</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D126" t="str">
         <v>2026-04-18</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H126" t="str">
-        <v>The Kid LAROI</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L126" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Wannabeher</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D127" t="str">
         <v>2026-04-18</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Dancing On The Wall</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H127" t="str">
-        <v>MUNA</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L127" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Superbloom</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D128" t="str">
         <v>2026-04-18</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Superbloom</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G128" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H128" t="str">
-        <v>Jessie Ware</v>
+        <v>MUNA</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L128" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Chairwoman Park</v>
+        <v>Superbloom</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D129" t="str">
         <v>2026-04-18</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G129" t="str">
-        <v>1:40</v>
+        <v>4:11</v>
       </c>
       <c r="H129" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L129" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Make You Move</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D130" t="str">
         <v>2026-04-18</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Make You Move - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G130" t="str">
-        <v>2:24</v>
+        <v>1:40</v>
       </c>
       <c r="H130" t="str">
-        <v>Dillon Francis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L130" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>FERRARI</v>
+        <v>Make You Move</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D131" t="str">
         <v>2026-04-18</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>FERRARI - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H131" t="str">
-        <v>Clave Especial</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L131" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Por Ella</v>
+        <v>FERRARI</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D132" t="str">
         <v>2026-04-18</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L132" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D133" t="str">
         <v>2026-04-18</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H133" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L133" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D134" t="str">
         <v>2026-04-18</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G134" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H134" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L134" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D135" t="str">
         <v>2026-04-18</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H135" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L135" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D136" t="str">
         <v>2026-04-18</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G136" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H136" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L136" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D137" t="str">
         <v>2026-04-18</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G137" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H137" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L137" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D138" t="str">
         <v>2026-04-18</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H138" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L138" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D139" t="str">
         <v>2026-04-18</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G139" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H139" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L139" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D140" t="str">
         <v>2026-04-18</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H140" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L140" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D141" t="str">
         <v>2026-04-18</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H141" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L141" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D142" t="str">
         <v>2026-04-18</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G142" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H142" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L142" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D143" t="str">
         <v>2026-04-18</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G143" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H143" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L143" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D144" t="str">
         <v>2026-04-18</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G144" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H144" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L144" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D145" t="str">
         <v>2026-04-18</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H145" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L145" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D146" t="str">
         <v>2026-04-18</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G146" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H146" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L146" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D147" t="str">
         <v>2026-04-18</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H147" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L147" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D148" t="str">
         <v>2026-04-18</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G148" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H148" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L148" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D149" t="str">
         <v>2026-04-18</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H149" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L149" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D150" t="str">
         <v>2026-04-18</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H150" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L150" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D151" t="str">
         <v>2026-04-18</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H151" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L151" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D152" t="str">
         <v>2026-04-18</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G152" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H152" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L152" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D153" t="str">
         <v>2026-04-18</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G153" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H153" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L153" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D154" t="str">
         <v>2026-04-18</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G154" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H154" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L154" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D155" t="str">
         <v>2026-04-18</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G155" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H155" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L155" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D156" t="str">
         <v>2026-04-18</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G156" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H156" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L156" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D157" t="str">
         <v>2026-04-18</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H157" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L157" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D158" t="str">
         <v>2026-04-18</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G158" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H158" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L158" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D159" t="str">
         <v>2026-04-18</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H159" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L159" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D160" t="str">
         <v>2026-04-18</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G160" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H160" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L160" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D161" t="str">
         <v>2026-04-18</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H161" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L161" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D162" t="str">
         <v>2026-04-18</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H162" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L162" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D163" t="str">
         <v>2026-04-18</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H163" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L163" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D164" t="str">
         <v>2026-04-18</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G164" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H164" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L164" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D165" t="str">
         <v>2026-04-18</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H165" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L165" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D166" t="str">
         <v>2026-04-18</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H166" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L166" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D167" t="str">
         <v>2026-04-18</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G167" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H167" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L167" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D168" t="str">
         <v>2026-04-18</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G168" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H168" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L168" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D169" t="str">
         <v>2026-04-18</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H169" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L169" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D170" t="str">
         <v>2026-04-18</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H170" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L170" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D171" t="str">
         <v>2026-04-18</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H171" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L171" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D172" t="str">
         <v>2026-04-18</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H172" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L172" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D173" t="str">
         <v>2026-04-18</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G173" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H173" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L173" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D174" t="str">
         <v>2026-04-18</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H174" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L174" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D175" t="str">
         <v>2026-04-18</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G175" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H175" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L175" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D176" t="str">
         <v>2026-04-18</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G176" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H176" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L176" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D177" t="str">
         <v>2026-04-18</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H177" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L177" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D178" t="str">
         <v>2026-04-18</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H178" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L178" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D179" t="str">
         <v>2026-04-18</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H179" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L179" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D180" t="str">
         <v>2026-04-18</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H180" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L180" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D181" t="str">
         <v>2026-04-18</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H181" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L181" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D182" t="str">
         <v>2026-04-18</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H182" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L182" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D183" t="str">
         <v>2026-04-18</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G183" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H183" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L183" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D184" t="str">
         <v>2026-04-18</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G184" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H184" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L184" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D185" t="str">
         <v>2026-04-18</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H185" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L185" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D186" t="str">
         <v>2026-04-18</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H186" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L186" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D187" t="str">
         <v>2026-04-18</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G187" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H187" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L187" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D188" t="str">
         <v>2026-04-18</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G188" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H188" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L188" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D189" t="str">
         <v>2026-04-18</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H189" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L189" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D190" t="str">
         <v>2026-04-18</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G190" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H190" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L190" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D191" t="str">
         <v>2026-04-18</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H191" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L191" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D192" t="str">
         <v>2026-04-18</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H192" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L192" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D193" t="str">
         <v>2026-04-18</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G193" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L193" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D194" t="str">
         <v>2026-04-18</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H194" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L194" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D195" t="str">
         <v>2026-04-18</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H195" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L195" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D196" t="str">
         <v>2026-04-18</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G196" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H196" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L196" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D197" t="str">
         <v>2026-04-18</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L197" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D198" t="str">
         <v>2026-04-18</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H198" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L198" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D199" t="str">
         <v>2026-04-18</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H199" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L199" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D200" t="str">
         <v>2026-04-18</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H200" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L200" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G201" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H201" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>3:32</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -743,7 +743,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B2" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-18</v>
@@ -457,7 +457,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Lana Del Rey</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B3" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-18</v>
@@ -495,7 +495,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Loreen</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-18</v>
@@ -533,7 +533,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-18</v>
@@ -571,7 +571,7 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Tenille Townes</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-18</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>ERNEST</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-18</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Danna</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-18</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>OneRepublic</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-18</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Revivalists</v>
+        <v>Bella White</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-18</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>James Smith</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-18</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Holly Humberstone</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-18</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ava Max</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-18</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>John Summit</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-18</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Ava Max</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-18</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Danna</v>
+        <v>Tyla</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-18</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Conan Gray</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-18</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>TemplesOfficial</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-18</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Laufey</v>
+        <v>Loreen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-18</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>bleachers</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-18</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-18</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>LANY</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-18</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Danna</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-18</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-18</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-18</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Kygo and carter faith</v>
+        <v>James Smith</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Official Video) - Kygo and carter faith</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-18</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>florencemachine</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-18</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Scorpions</v>
+        <v>Ava Max</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-18</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Holly Humberstone</v>
+        <v>John Summit</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-18</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>HAUSER</v>
+        <v>Ava Max</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-18</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Holly Humberstone</v>
+        <v>Danna</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-18</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-18</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Mae Muller</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-18</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Dead Pony</v>
+        <v>Laufey</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-18</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Nothing But Thieves</v>
+        <v>bleachers</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-18</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>kenzie - where do we go</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-18</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>kenzie</v>
+        <v>LANY</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-18</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-18</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Laufey</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-18</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Ella Langley</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-18</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Mei Semones</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-18</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Evanescence</v>
+        <v>florencemachine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-18</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>elijah woods</v>
+        <v>Scorpions</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-18</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>colby!</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B44" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-18</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>The Chainsmokers</v>
+        <v>HAUSER</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-18</v>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>aron!</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B46" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-18</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Owen Riegling</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-18</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-18</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Teddy Swims</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-18</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-18</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-18</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Sunday (1994)</v>
+        <v>kenzie</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-18</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-18</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Freya Skye</v>
+        <v>Laufey</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-18</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Bryan Adams</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-18</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>We Three</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-18</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Evanescence</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-18</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Bebe Rexha</v>
+        <v>elijah woods</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-18</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>The Lemon Twigs</v>
+        <v>colby!</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-18</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>METTE</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-18</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Saint Harison</v>
+        <v>aron!</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-18</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>NewDad</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-18</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Danna</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-18</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>florencemachine</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-18</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>HYBE LABELS</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-18</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Kungs</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-18</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Charlie Puth</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-18</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Nothing But Thieves</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B68" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-18</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B69" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-18</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Madison Cunningham</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B70" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-18</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>13 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Armin van Buuren</v>
+        <v>We Three</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-18</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-18</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-18</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Ocean Alley</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-18</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>RAYE</v>
+        <v>METTE</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-18</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Take That</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B76" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-18</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Armik</v>
+        <v>NewDad</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-18</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Switchfoot</v>
+        <v>Danna</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-18</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Peter Gabriel</v>
+        <v>florencemachine</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B79" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-18</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Sarah Julia</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-18</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Chris Norman</v>
+        <v>Kungs</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B81" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-18</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Alan Walker</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-18</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Charlie Puth</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B83" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-18</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Miley Cyrus</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B84" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-18</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Conan Gray</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B85" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-18</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Charlie Puth</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-18</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Kylie Morgan</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=V9xtQsL89ws</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-18</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Ricky Martin and 2 more</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ricky Martin, Los Ángeles Azules, TINI - Vuelve (Official Video) - Ricky Martin and 2 more</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=WJn_qS51hi0</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-18</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Angelina Mango</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Angelina Mango - che t'o dico a fa' (caramé live version) - Angelina Mango</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie)</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NyLqdtFPrcM</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-18</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Julio Iglesias</v>
+        <v>RAYE</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Julio Iglesias - Nathalie (Nathalie) - Julio Iglesias</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loreen - Coming Close (Official Music Video)</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=jz3Ok5A2nZk</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-18</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Loreen</v>
+        <v>Take That</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Loreen - Coming Close (Official Music Video) - Loreen</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jessie Ware - Automatic</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B91" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=y35H9XrTpfE</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-18</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Jessie Ware</v>
+        <v>Armik</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Jessie Ware - Automatic - Jessie Ware</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=SooS_mBKaC4</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-18</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Holly Humberstone and Life is Strange</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Holly Humberstone - Embers In The Sky (Official 'LIFE IS STRANGE: REUNION' Visualiser) - Holly Humberstone and Life is Strange</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B93" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lnwUQQaDOsM</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-18</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions)</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=R38wB_dDBek</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-18</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Ella Langley</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ella Langley - Loving Life Again (Back Home Sessions) - Ella Langley</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Eagles - One Of These Nights (Official Audio)</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=i6ABSANz6kA</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-18</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eagles</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Eagles - One Of These Nights (Official Audio) - Eagles</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B96" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=5YuhFClIBzQ</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-18</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Moody Joody</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Moody Joody - Loretta's Last Call (Official Video) - Moody Joody</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video)</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B97" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=xSeLB6r8mP4</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-18</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Jackson Dean</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jackson Dean - Hey Mississippi (Lyric Video) - Jackson Dean</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B98" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=osOoVUM2Owg</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-18</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>John Summit and The Chainsmokers</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>John Summit, The Chainsmokers, Ilsey - ALL THE TIME (Official Visualizer) - John Summit and The Chainsmokers</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas)</v>
+        <v>Conan Gray - The Best (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=iaXLST2vNH0</v>
+        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-18</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Madison Cunningham</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Madison Cunningham - Break The Jaw (Live in Dallas) - Madison Cunningham</v>
+        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>mary in the junkyard - Crash Landing (Official)</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=vYWFjdiSbPU</v>
+        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-18</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>mary in the junkyard</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>mary in the junkyard - Crash Landing (Official) - mary in the junkyard</v>
+        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video)</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=AZDMA1M-rKY</v>
+        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-18</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Adam Sanders</v>
+        <v>Kylie Morgan</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Adam Sanders - Bible in a House Fire (Official Music Video) - Adam Sanders</v>
+        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-18</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Peter Gabriel</v>
+        <v>Madonna</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-18</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-18</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Jessie Ware</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-18</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-18</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>ERNEST</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-18</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Jessie Ware - Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-18</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Dean Lewis</v>
+        <v>The Kid LAROI.</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-18</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Bella White</v>
+        <v>ERNEST</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-18</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Kip Moore</v>
+        <v>DisneyMusicVEVO</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-18</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-18</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Ben Gallaher</v>
+        <v>Bella White</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
+        <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
+        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-18</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Reservoir Recordings</v>
+        <v>Kip Moore</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
+        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video)</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
+        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-18</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Johnny Orlando</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
+        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
+        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-18</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Tyla</v>
+        <v>Ben Gallaher</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
+        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
+        <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-18</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Reservoir Recordings</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
+        <v>Innocent Bystanders - Under Wraps (Official 4K Music Video) - Reservoir Recordings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video)</v>
+        <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
+        <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-18</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Lana Del Rey</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
+        <v>Johnny Orlando - Charlotte (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Loreen - True Love (Official Video)</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
+        <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-18</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Loreen</v>
+        <v>Tyla</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Loreen - True Love (Official Video) - Loreen</v>
+        <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson - Tyla</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
+        <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-18</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Bonnie Tyler</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
+        <v>Lewis Capaldi - Stay Love (Official Visualizer) - Lewis Capaldi</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
+        <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
+        <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-18</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Tenille Townes</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
+        <v>Lana Del Rey - First Light (Lyric Video) - Lana Del Rey</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Cream - White Room [Official Lyric Video]</v>
+        <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
+        <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-18</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Cream - Band and 2 more</v>
+        <v>Loreen</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
+        <v>Loreen - True Love (Official Video) - Loreen</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
+        <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-18</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Danna</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
+        <v>Bonnie Tyler - Only Love (Official Lyric Video) - Bonnie Tyler</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
+        <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-18</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>OneRepublic</v>
+        <v>Tenille Townes</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
+        <v>Tenille Townes - in love with the sky (Live Acoustic) - Tenille Townes</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video)</v>
+        <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
+        <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-18</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>The Revivalists</v>
+        <v>Cream - Band and 2 more</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
+        <v>Cream - White Room [Official Lyric Video] - Cream - Band and 2 more</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal)</v>
+        <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
+        <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-18</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>James Smith</v>
+        <v>Danna</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
+        <v>DANNA - YOU COULD BE THAT BOY - Danna</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
+        <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-18</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Holly Humberstone</v>
+        <v>OneRepublic</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
+        <v>OneRepublic – Need Your Love - LIVE ON TOUR - OneRepublic</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
+        <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
+        <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-18</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Ava Max</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
+        <v>The Revivalists - Heart Stop (Official Music Video) - The Revivalists</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>John Summit - STATUS:AWAY</v>
+        <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
+        <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-18</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>John Summit</v>
+        <v>James Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>John Summit - STATUS:AWAY - John Summit</v>
+        <v>My Angels - James Smith (Live Band Rehearsal) - James Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
+        <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-18</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Ava Max</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
+        <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!") - Holly Humberstone</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DANNA - AGAIN (Lyric Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
+        <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-18</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Danna</v>
+        <v>Ava Max</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
+        <v>Ava Max - Out Of Your Mind (Official Lyric Video) - Ava Max</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
+        <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
+        <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-18</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Conan Gray</v>
+        <v>John Summit</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
+        <v>John Summit - STATUS:AWAY - John Summit</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Temples - Vendetta (Official Video)</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
+        <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-18</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>TemplesOfficial</v>
+        <v>Ava Max</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
+        <v>Ava Max - Out Of Your Mind (Official Audio) - Ava Max</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Laufey - Madwoman (Official Music Video)</v>
+        <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
+        <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-18</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Laufey</v>
+        <v>Danna</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
+        <v>DANNA - AGAIN (Lyric Video) - Danna</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bleachers - the van (Official Music Video)</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
+        <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-18</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>bleachers</v>
+        <v>Conan Gray</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bleachers - the van (Official Music Video) - bleachers</v>
+        <v>Conan Gray - The Best (Live at the Kia Forum) - Conan Gray</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
+        <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
+        <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-18</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Nothing But Thieves</v>
+        <v>TemplesOfficial</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
+        <v>Temples - Vendetta (Official Video) - TemplesOfficial</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
+        <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-18</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>LANY</v>
+        <v>Laufey</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
+        <v>Laufey - Madwoman (Official Music Video) - Laufey</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
+        <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
+        <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-18</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>bleachers</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Bleachers - the van (Official Music Video) - bleachers</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
+        <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-18</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Coachella and Sabrina Carpenter</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
+        <v>Nothing But Thieves - Before We Drift Away (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
+        <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-18</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>keshi and AT&amp;T</v>
+        <v>LANY</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
+        <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video) - LANY</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
+        <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-18</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Kygo and carter faith</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kygo, Carter Faith - That's When You Know (Official Video) - Kygo and carter faith</v>
+        <v>Sabrina Carpenter - House Tour - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video)</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
+        <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-18</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>florencemachine</v>
+        <v>Coachella and Sabrina Carpenter</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
+        <v>Sabrina Carpenter - Espresso - Live at Coachella 2026 - Coachella and Sabrina Carpenter</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
+        <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-18</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Scorpions</v>
+        <v>keshi and AT&amp;T</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
+        <v>keshi - "summer" Live at AT&amp;T Block Party 2026 - keshi and AT&amp;T</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
+        <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-18</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Holly Humberstone</v>
+        <v>Kygo and carter faith</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
+        <v>Kygo, Carter Faith - That's When You Know (Official Video) - Kygo and carter faith</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>HAUSER - Pavane</v>
+        <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
+        <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-18</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>HAUSER</v>
+        <v>florencemachine</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>HAUSER - Pavane - HAUSER</v>
+        <v>Florence + The Machine - And Love (Lyric Video) - florencemachine</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video)</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
+        <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-18</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Holly Humberstone</v>
+        <v>Scorpions</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
+        <v>Scorpions - Seventh Sun (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>YES - Aurora (Official Video)</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
+        <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-18</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
+        <v>Holly Humberstone - Beauty Pageant (Official Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video)</v>
+        <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
+        <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-18</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mae Muller</v>
+        <v>HAUSER</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
+        <v>HAUSER - Pavane - HAUSER</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
+        <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
+        <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-18</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Dead Pony</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
+        <v>Holly Humberstone - White Noise (Lyric Video) - Holly Humberstone</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
+        <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
+        <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-18</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Nothing But Thieves</v>
+        <v>yesofficial and InsideOutMusicTV</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
+        <v>YES - Aurora (Official Video) - yesofficial and InsideOutMusicTV</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
+        <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
+        <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-18</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Jennifer Lopez</v>
+        <v>Mae Muller</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
+        <v>Mae Muller - Tell You That (Official Music Video) - Mae Muller</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>kenzie - where do we go</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
+        <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-18</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>kenzie</v>
+        <v>Dead Pony</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>kenzie - where do we go - kenzie</v>
+        <v>Dead Pony - Freak Like Me (Official Music Video) - Dead Pony</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video)</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
+        <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-18</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Foo Fighters</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
+        <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
+        <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-18</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Laufey</v>
+        <v>Jennifer Lopez</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
+        <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish) - Jennifer Lopez</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
+        <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
+        <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-18</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Ella Langley</v>
+        <v>kenzie</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
+        <v>kenzie - where do we go - kenzie</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
+        <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
+        <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-18</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Mei Semones</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
+        <v>Foo Fighters - Of All People (Lyric Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
+        <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-18</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Evanescence</v>
+        <v>Laufey</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
+        <v>Laufey - Madwoman (Official Lyric Video with Chords) - Laufey</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions)</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
+        <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-18</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>elijah woods</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
+        <v>Ella Langley - Somethin' Simple (Official Audio) - Ella Langley</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
+        <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-18</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>colby!</v>
+        <v>Mei Semones</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
+        <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer) - Mei Semones</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
+        <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-18</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The Chainsmokers</v>
+        <v>Evanescence</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
+        <v>Evanescence - Who Will You Follow (Official Lyric Video) - Evanescence</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>aron! - Foolsong (Guitar)</v>
+        <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
+        <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-18</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>aron!</v>
+        <v>elijah woods</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>aron! - Foolsong (Guitar) - aron!</v>
+        <v>elijah woods - DNA (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Owen Riegling - Anything But Me</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
+        <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-18</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Owen Riegling</v>
+        <v>colby!</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
+        <v>colby! - Who's Your Angel Now (Official Music Video) - colby!</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
+        <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-18</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Lainey Wilson and Nova's Red Room</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
+        <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Teddy Swims - Mr. Know It All</v>
+        <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
+        <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-18</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Teddy Swims</v>
+        <v>aron!</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
+        <v>aron! - Foolsong (Guitar) - aron!</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
+        <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
+        <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-18</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>BEAUTY SCHOOL DROPOUT</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
+        <v>Owen Riegling - Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
+        <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-18</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>Lainey Wilson and Nova's Red Room</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session - Lainey Wilson and Nova's Red Room</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Sunday (1994) - Shame (Official Video)</v>
+        <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
+        <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-18</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Sunday (1994)</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
+        <v>Teddy Swims - Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
+        <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-18</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
+        <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video) - BEAUTY SCHOOL DROPOUT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
+        <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-18</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Freya Skye</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
+        <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
+        <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-18</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Bryan Adams</v>
+        <v>Sunday (1994)</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
+        <v>Sunday (1994) - Shame (Official Video) - Sunday (1994)</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>We Three - New Zealand (Live Sessions)</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
+        <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-18</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>We Three</v>
+        <v>twenty one pilots and AT&amp;T</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>We Three - New Zealand (Live Sessions) - We Three</v>
+        <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026) - twenty one pilots and AT&amp;T</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
+        <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-18</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Freya Skye</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
+        <v>Freya Skye - silent treatment (Stars Align Tour: Live from London) - Freya Skye</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual)</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
+        <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-18</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Bebe Rexha</v>
+        <v>Bryan Adams</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
+        <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film - Bryan Adams</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
+        <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
+        <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-18</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>The Lemon Twigs</v>
+        <v>We Three</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
+        <v>We Three - New Zealand (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>METTE - COMING OF AGE (Official Video)</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
+        <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-18</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>METTE</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
+        <v>Dermot Kennedy - Turnstile (Live From Glenmaroon) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Saint Harison - stuck (Official Music Video)</v>
+        <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
+        <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-18</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Saint Harison</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
+        <v>Bebe Rexha - Hysteria (Official Visual) - Bebe Rexha</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Newdad - Kick The Curb</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
+        <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-18</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>NewDad</v>
+        <v>The Lemon Twigs</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Newdad - Kick The Curb - NewDad</v>
+        <v>The Lemon Twigs - 2 or 3 (Official Video) - The Lemon Twigs</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DANNA - LUCID (Visualizer)</v>
+        <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
+        <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-18</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Danna</v>
+        <v>METTE</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DANNA - LUCID (Visualizer) - Danna</v>
+        <v>METTE - COMING OF AGE (Official Video) - METTE</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
+        <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
+        <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-18</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>florencemachine</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
+        <v>Saint Harison - stuck (Official Music Video) - Saint Harison</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
+        <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
+        <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-18</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>HYBE LABELS</v>
+        <v>NewDad</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
+        <v>Newdad - Kick The Curb - NewDad</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
+        <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
+        <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-18</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Kungs</v>
+        <v>Danna</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
+        <v>DANNA - LUCID (Visualizer) - Danna</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
+        <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-18</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Charlie Puth</v>
+        <v>florencemachine</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
+        <v>Florence + The Machine - You Can Have It All (Visualiser) - florencemachine</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
+        <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-18</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Nothing But Thieves</v>
+        <v>HYBE LABELS</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
+        <v>BTS (방탄소년단) 'Hooligan' Official MV - HYBE LABELS</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
+        <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-18</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Kungs</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
+        <v>Kungs, Stevie Appleton - Body Talk (Visualizer) - Kungs</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
+        <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-18</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Madison Cunningham</v>
+        <v>Charlie Puth</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
+        <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint - Charlie Puth</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
+        <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-18</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Armin van Buuren</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Nothing But Thieves - There Was Sun (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
+        <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-18</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
+        <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show - SIENNA SPIRO and The Jonathan Ross Show</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
+        <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-18</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
+        <v>Madison Cunningham - Hospital (Live at Big Ears Festival) - Madison Cunningham</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
+        <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-18</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Ocean Alley</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
+        <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
+        <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
+        <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-18</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>RAYE</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
+        <v>Sabrina Carpenter - House Tour (Official Video) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Take That - You're A Superstar (Lyric Video)</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
+        <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-18</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Take That</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
+        <v>Nothing But Thieves - Free If We Want It (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
+        <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-18</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Armik</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO) - Ocean Alley</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
+        <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-18</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Switchfoot</v>
+        <v>RAYE</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
+        <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios) - RAYE</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
+        <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
+        <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-18</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Peter Gabriel</v>
+        <v>Take That</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
+        <v>Take That - You're A Superstar (Lyric Video) - Take That</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
+        <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-18</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Sarah Julia</v>
+        <v>Armik</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
+        <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video)</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
+        <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-18</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Chris Norman</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
+        <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video) - Switchfoot</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
+        <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-18</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Alan Walker</v>
+        <v>Peter Gabriel</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
+        <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour) - Peter Gabriel</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
+        <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-18</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Charlie Puth</v>
+        <v>Sarah Julia</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
+        <v>Sarah Julia - Bigger Picture (Official Lyric Video) - Sarah Julia</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
+        <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-18</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Miley Cyrus</v>
+        <v>Chris Norman</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>Chris Norman - Addicted To Love (Official Video) - Chris Norman</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conan Gray - The Best (Lyric Video)</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Fk9FSZo2geg</v>
+        <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-18</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Conan Gray</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Conan Gray - The Best (Lyric Video) - Conan Gray</v>
+        <v>Alan Walker, Emyrson Flora - Monster (Official Music Video) - Alan Walker</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer]</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=5ztBxLRJHWw</v>
+        <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-18</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Charlie Puth - New Jersey (feat. Ravyn Lenae) [Official Visualizer] - Charlie Puth</v>
+        <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer] - Charlie Puth</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video)</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=3U7XggRnyHI</v>
+        <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-18</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Kylie Morgan</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Kylie Morgan - 1-(800) Dump Him (Official Video) - Kylie Morgan</v>
+        <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>8h ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8h ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 hours ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>11 hours ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>16h ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>16h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>16h ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16h ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B5" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Innocent Bystanders - Under Wraps (Official 4K Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=eJkakF1P8Ds</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Johnny Orlando - Charlotte (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Y5bX0ZJmPEA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Tyla - SHE DID IT AGAIN (Official Music Video) ft. Zara Larsson</v>
       </c>
       <c r="B18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=rtwpk9rb1Dc</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Lewis Capaldi - Stay Love (Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=hLWLS-Csppw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Lana Del Rey - First Light (Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=fA82c4YkAZ4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Loreen - True Love (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=aPG0juqEAEU</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Bonnie Tyler - Only Love (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=T_NLATFJ5Zo</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Tenille Townes - in love with the sky (Live Acoustic)</v>
       </c>
       <c r="B23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=teJOGC-8tzo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Cream - White Room [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=-DQdB7dTm1A</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>DANNA - YOU COULD BE THAT BOY</v>
       </c>
       <c r="B25" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6XUcwGlLwBs</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>OneRepublic – Need Your Love - LIVE ON TOUR</v>
       </c>
       <c r="B26" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=UolrFUwIl_8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Revivalists - Heart Stop (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=MxYpjjaAeFE</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>My Angels - James Smith (Live Band Rehearsal)</v>
       </c>
       <c r="B28" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=1k-Zlrpw-MA</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Holly Humberstone - Beauty Pageant (Live On "Jimmy Kimmel Live!")</v>
       </c>
       <c r="B29" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=Vk6M6n_xPVY</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Ava Max - Out Of Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=uH2u4i-EqPs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>John Summit - STATUS:AWAY</v>
       </c>
       <c r="B31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=p63BsBmPDyo</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ava Max - Out Of Your Mind (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=a6sBrkLUY-8</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>DANNA - AGAIN (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=YYUVDCClJZ0</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Conan Gray - The Best (Live at the Kia Forum)</v>
       </c>
       <c r="B34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Seoce9ajf3U</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Temples - Vendetta (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=j4j5zPsiNOk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>Laufey - Madwoman (Official Music Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=yNa8jP4zoJo</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Bleachers - the van (Official Music Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=z28Pgx8yCm0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Nothing But Thieves - Before We Drift Away (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=AmV7oYeYi_Q</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>LANY - Prettiest Thing I've Ever Seen (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=_nRzDvk1Yrg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Sabrina Carpenter - House Tour - Live at Coachella 2026</v>
       </c>
       <c r="B40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=x5qCbLcWgps</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Sabrina Carpenter - Espresso - Live at Coachella 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=hp5O72WUqTk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>keshi - "summer" Live at AT&amp;T Block Party 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=bM6aXOF0Tdk</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Kygo, Carter Faith - That's When You Know (Official Video)</v>
       </c>
       <c r="B43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=OrFCmaZLKGw</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Florence + The Machine - And Love (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=2naNoPmhUCo</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Scorpions - Seventh Sun (Madison Square Garden 2022)</v>
       </c>
       <c r="B45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=fSs5C8L2fAQ</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>Holly Humberstone - Beauty Pageant (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=l3cedY9fE_g</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>HAUSER - Pavane</v>
       </c>
       <c r="B47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=7WinkEjnLOk</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Holly Humberstone - White Noise (Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=3tbd3ap_1B4</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>YES - Aurora (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ETEGJTM6plw</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Mae Muller - Tell You That (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=uvwiMNv2Ffc</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Dead Pony - Freak Like Me (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=q39uDJzvFok</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>Nothing But Thieves - Futureproof (Live from TRNSMT Festival, 2023)</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=BD5SPu_mI_g</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>Jennifer Lopez - Amor Se Paga Con Amor (Love Don't Cost A Thing) (spanglish)</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=Ackb-Ll_F8w</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>kenzie - where do we go</v>
       </c>
       <c r="B54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=-FcaJwD3hAk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>Foo Fighters - Of All People (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=rD8Gtp2r6t4</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>Laufey - Madwoman (Official Lyric Video with Chords)</v>
       </c>
       <c r="B56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=R_J3pz33Qwc</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Ella Langley - Somethin' Simple (Official Audio)</v>
       </c>
       <c r="B57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=D7YVFFIT6Kg</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Mei Semones - Kurage ft. Don Semones (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=5cZUfyVczB4</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Evanescence - Who Will You Follow (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=MoNhLJKLAyQ</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>elijah woods - DNA (Treehouse Sessions)</v>
       </c>
       <c r="B60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=7axhhkaxPrs</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>colby! - Who's Your Angel Now (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=-wCVPhXSysM</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Chainsmokers - Echo ft. Oaks (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=5-NfPGEyi-c</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>aron! - Foolsong (Guitar)</v>
       </c>
       <c r="B63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=JfBx7P-6MoI</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Owen Riegling - Anything But Me</v>
       </c>
       <c r="B64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Xps0cMZZV3k</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Lainey Wilson - Can't Sit Still | Nova’s Red Room Studio Session</v>
       </c>
       <c r="B65" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=_rkXumZzU4U</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Teddy Swims - Mr. Know It All</v>
       </c>
       <c r="B66" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=KllnaNOxe0I</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>BEAUTY SCHOOL DROPOUT - DADDY DON'T CRY (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=kgojdaCvgNU</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Twenty One Pilots - Tally (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B68" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=hxVomy11nc0</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Sunday (1994) - Shame (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=ngb0Dkwpzi0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Twenty One Pilots - Drag Path (AT&amp;T Block Party 2026)</v>
       </c>
       <c r="B70" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=pQZKEP1b-Vs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Freya Skye - silent treatment (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=z1CyV1hSl0Y</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Bryan Adams - So Happy It Hurts / 2024 Pre Concert film</v>
       </c>
       <c r="B72" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=qAsTsu5Xv5o</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>We Three - New Zealand (Live Sessions)</v>
       </c>
       <c r="B73" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=DDN52Sm075g</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Dermot Kennedy - Turnstile (Live From Glenmaroon)</v>
       </c>
       <c r="B74" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=C19qERI5bX0</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Bebe Rexha - Hysteria (Official Visual)</v>
       </c>
       <c r="B75" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=TGEYho8ucHo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>The Lemon Twigs - 2 or 3 (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=T1sHIzZYxfY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>METTE - COMING OF AGE (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=9YYMZa5rImQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Saint Harison - stuck (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ae8t8jJn92E</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Newdad - Kick The Curb</v>
       </c>
       <c r="B79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=3srL8VwkezU</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>DANNA - LUCID (Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=LWYUhQqbtK0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Florence + The Machine - You Can Have It All (Visualiser)</v>
       </c>
       <c r="B81" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=sprHv43e5iY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>BTS (방탄소년단) 'Hooligan' Official MV</v>
       </c>
       <c r="B82" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=diBO0gMuTXo</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Kungs, Stevie Appleton - Body Talk (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=LQCmtZYzdcA</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Charlie Puth - Beat Yourself Up | Amazon Music presents: In The Paint</v>
       </c>
       <c r="B84" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=t2LsND_R8AA</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Nothing But Thieves - There Was Sun (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=r-qb5NEKStU</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>SIENNA SPIRO - The Visitor | The Jonathan Ross Show</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=oG1S2QXHnOQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>Madison Cunningham - Hospital (Live at Big Ears Festival)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=8V5XYV5bq58</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Armin van Buuren - Waltz (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=aWUtMkqbfzI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Sabrina Carpenter - House Tour (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=KWoTyfPsqbE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Nothing But Thieves - Free If We Want It (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=9_liimIqqgI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>OCEAN ALLEY - JELLYFISH (OFFICIAL AUDIO)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=3vLOBvmuOYw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>RAYE - I Know You’re Hurting. (Live at Abbey Road Studios)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=NXkn1Ee7Q5o</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Take That - You're A Superstar (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=cbMBD9boh1Q</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Armik - Calima (Uplifting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=IDkllYpc0VY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Switchfoot - Wake Up, Mr. Crow (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=CSzk_d3ZWZA</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Peter Gabriel What Lies Ahead (live in Verona - i/o The Tour)</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=ApQ3PDyemEM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Sarah Julia - Bigger Picture (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=xn5TR7wFEjk</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Chris Norman - Addicted To Love (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=pXrZW51t8nk</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Alan Walker, Emyrson Flora - Monster (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=vv0YJOY5txc</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>Charlie Puth - Sideways (feat. Coco Jones) [Official Visualizer]</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=wGVBXutyyuY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Miley Cyrus - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=s-dr_KJvmO4</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E202" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-04-week03/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@